--- a/research/traditional_assets/database/data/peru/peru_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_shipbuilding_marine.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvl_aihc1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.322</v>
+        <v>-0.158</v>
       </c>
       <c r="G2">
-        <v>-0.2530701754385964</v>
+        <v>0.07379912663755459</v>
       </c>
       <c r="H2">
-        <v>-0.2530701754385964</v>
+        <v>0.07379912663755459</v>
       </c>
       <c r="I2">
-        <v>-0.05482456140350877</v>
+        <v>0.1013100436681223</v>
       </c>
       <c r="J2">
-        <v>-0.04293281556326346</v>
+        <v>0.05766510068503074</v>
       </c>
       <c r="K2">
-        <v>1.17</v>
+        <v>12</v>
       </c>
       <c r="L2">
-        <v>0.0513157894736842</v>
+        <v>0.1746724890829694</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.02</v>
+        <v>11.6</v>
       </c>
       <c r="V2">
-        <v>0.2166666666666667</v>
+        <v>0.3213296398891967</v>
       </c>
       <c r="W2">
-        <v>0.005687894992707827</v>
+        <v>0.06204756980351603</v>
       </c>
       <c r="X2">
-        <v>0.1140780340754432</v>
+        <v>0.2171573874656431</v>
       </c>
       <c r="Y2">
-        <v>-0.1083901390827353</v>
+        <v>-0.155109817662127</v>
       </c>
       <c r="Z2">
-        <v>0.09954853864491736</v>
+        <v>0.3172917051542583</v>
       </c>
       <c r="AA2">
-        <v>-0.004273899049234642</v>
+        <v>0.01829665812424539</v>
       </c>
       <c r="AB2">
-        <v>0.06904761572335037</v>
+        <v>0.1226322152218451</v>
       </c>
       <c r="AC2">
-        <v>-0.07332151477258501</v>
+        <v>-0.1043355570975998</v>
       </c>
       <c r="AD2">
-        <v>36.7</v>
+        <v>48.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>36.7</v>
+        <v>48.7</v>
       </c>
       <c r="AG2">
-        <v>29.68</v>
+        <v>37.1</v>
       </c>
       <c r="AH2">
-        <v>0.5311143270622287</v>
+        <v>0.5742924528301886</v>
       </c>
       <c r="AI2">
-        <v>0.1594958713602781</v>
+        <v>0.1760028912179256</v>
       </c>
       <c r="AJ2">
-        <v>0.4780927835051547</v>
+        <v>0.5068306010928961</v>
       </c>
       <c r="AK2">
-        <v>0.1330464407387484</v>
+        <v>0.1399471897397208</v>
       </c>
       <c r="AL2">
-        <v>4.15</v>
+        <v>5.77</v>
       </c>
       <c r="AM2">
-        <v>3.936</v>
+        <v>5.593</v>
       </c>
       <c r="AN2">
-        <v>111.5501519756839</v>
+        <v>4.821782178217823</v>
       </c>
       <c r="AO2">
-        <v>-0.3012048192771084</v>
+        <v>1.206239168110919</v>
       </c>
       <c r="AP2">
-        <v>90.21276595744682</v>
+        <v>3.673267326732673</v>
       </c>
       <c r="AQ2">
-        <v>-0.3175813008130081</v>
+        <v>1.244412658680494</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.322</v>
+        <v>-0.158</v>
       </c>
       <c r="G3">
-        <v>-0.2530701754385964</v>
+        <v>0.07379912663755459</v>
       </c>
       <c r="H3">
-        <v>-0.2530701754385964</v>
+        <v>0.07379912663755459</v>
       </c>
       <c r="I3">
-        <v>-0.05482456140350877</v>
+        <v>0.1013100436681223</v>
       </c>
       <c r="J3">
-        <v>-0.04293281556326346</v>
+        <v>0.05766510068503074</v>
       </c>
       <c r="K3">
-        <v>1.17</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>0.0513157894736842</v>
+        <v>0.1746724890829694</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.02</v>
+        <v>11.6</v>
       </c>
       <c r="V3">
-        <v>0.2166666666666667</v>
+        <v>0.3213296398891967</v>
       </c>
       <c r="W3">
-        <v>0.005687894992707827</v>
+        <v>0.06204756980351603</v>
       </c>
       <c r="X3">
-        <v>0.1140780340754432</v>
+        <v>0.2171573874656431</v>
       </c>
       <c r="Y3">
-        <v>-0.1083901390827353</v>
+        <v>-0.155109817662127</v>
       </c>
       <c r="Z3">
-        <v>0.09954853864491736</v>
+        <v>0.3172917051542583</v>
       </c>
       <c r="AA3">
-        <v>-0.004273899049234642</v>
+        <v>0.01829665812424539</v>
       </c>
       <c r="AB3">
-        <v>0.06904761572335037</v>
+        <v>0.1226322152218451</v>
       </c>
       <c r="AC3">
-        <v>-0.07332151477258501</v>
+        <v>-0.1043355570975998</v>
       </c>
       <c r="AD3">
-        <v>36.7</v>
+        <v>48.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>36.7</v>
+        <v>48.7</v>
       </c>
       <c r="AG3">
-        <v>29.68</v>
+        <v>37.1</v>
       </c>
       <c r="AH3">
-        <v>0.5311143270622287</v>
+        <v>0.5742924528301886</v>
       </c>
       <c r="AI3">
-        <v>0.1594958713602781</v>
+        <v>0.1760028912179256</v>
       </c>
       <c r="AJ3">
-        <v>0.4780927835051547</v>
+        <v>0.5068306010928961</v>
       </c>
       <c r="AK3">
-        <v>0.1330464407387484</v>
+        <v>0.1399471897397208</v>
       </c>
       <c r="AL3">
-        <v>4.15</v>
+        <v>5.77</v>
       </c>
       <c r="AM3">
-        <v>3.936</v>
+        <v>5.593</v>
       </c>
       <c r="AN3">
-        <v>111.5501519756839</v>
+        <v>4.821782178217823</v>
       </c>
       <c r="AO3">
-        <v>-0.3012048192771084</v>
+        <v>1.206239168110919</v>
       </c>
       <c r="AP3">
-        <v>90.21276595744682</v>
+        <v>3.673267326732673</v>
       </c>
       <c r="AQ3">
-        <v>-0.3175813008130081</v>
+        <v>1.244412658680494</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Andino Investment Holding S.A.A. (BVL:AIHC1)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVL:AIHC1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shipbuilding &amp; Marine</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.574292452830189</v>
+      </c>
+      <c r="F2">
+        <v>0.33</v>
+      </c>
+      <c r="G2">
+        <v>36.1</v>
+      </c>
+      <c r="H2">
+        <v>57.991008071082</v>
+      </c>
+      <c r="I2">
+        <v>73.2</v>
+      </c>
+      <c r="J2">
+        <v>74.37500807108199</v>
+      </c>
+      <c r="K2">
+        <v>48.7</v>
+      </c>
+      <c r="L2">
+        <v>27.984</v>
+      </c>
+      <c r="M2">
+        <v>0.122632215221845</v>
+      </c>
+      <c r="N2">
+        <v>0.121307798162176</v>
+      </c>
+      <c r="O2">
+        <v>0.052563247706422</v>
+      </c>
+      <c r="P2">
+        <v>0.038775</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.217157387465643</v>
+      </c>
+      <c r="T2">
+        <v>0.161958280839069</v>
+      </c>
+      <c r="U2">
+        <v>2.05644063137868</v>
+      </c>
+      <c r="V2">
+        <v>1.42000113596077</v>
+      </c>
+      <c r="W2">
+        <v>4.522064556369873</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>36.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.07455779816513761</v>
+      </c>
+      <c r="AD2">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>10.1</v>
+      </c>
+      <c r="AH2">
+        <v>3.14</v>
+      </c>
+      <c r="AI2">
+        <v>7.29</v>
+      </c>
+      <c r="AJ2">
+        <v>48.7</v>
+      </c>
+      <c r="AK2">
+        <v>48.7</v>
+      </c>
+      <c r="AL2">
+        <v>5.77</v>
+      </c>
+      <c r="AM2">
+        <v>48.7</v>
+      </c>
+      <c r="AN2">
+        <v>11.6</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1302153305956642</v>
+      </c>
+      <c r="C2">
+        <v>78.72788888092823</v>
+      </c>
+      <c r="D2">
+        <v>67.12788888092824</v>
+      </c>
+      <c r="E2">
+        <v>-48.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>11.6</v>
+      </c>
+      <c r="H2">
+        <v>36.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>10.1</v>
+      </c>
+      <c r="K2">
+        <v>3.14</v>
+      </c>
+      <c r="L2">
+        <v>6.96</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>6.96</v>
+      </c>
+      <c r="O2">
+        <v>2.053199999999999</v>
+      </c>
+      <c r="P2">
+        <v>4.9068</v>
+      </c>
+      <c r="Q2">
+        <v>8.046800000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1302153305956642</v>
+      </c>
+      <c r="T2">
+        <v>1.05400848733586</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.0322185</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.129879840370407</v>
+      </c>
+      <c r="C3">
+        <v>78.12715271527529</v>
+      </c>
+      <c r="D3">
+        <v>67.37515271527529</v>
+      </c>
+      <c r="E3">
+        <v>-47.852</v>
+      </c>
+      <c r="F3">
+        <v>0.8480000000000001</v>
+      </c>
+      <c r="G3">
+        <v>11.6</v>
+      </c>
+      <c r="H3">
+        <v>36.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>10.1</v>
+      </c>
+      <c r="K3">
+        <v>3.14</v>
+      </c>
+      <c r="L3">
+        <v>6.96</v>
+      </c>
+      <c r="M3">
+        <v>0.03875360000000001</v>
+      </c>
+      <c r="N3">
+        <v>6.9212464</v>
+      </c>
+      <c r="O3">
+        <v>2.041767688</v>
+      </c>
+      <c r="P3">
+        <v>4.879478712000001</v>
+      </c>
+      <c r="Q3">
+        <v>8.019478712000002</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1308663185559666</v>
+      </c>
+      <c r="T3">
+        <v>1.061514305351736</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.0322185</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>179.5962181577969</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1295443501451498</v>
+      </c>
+      <c r="C4">
+        <v>77.52824486398791</v>
+      </c>
+      <c r="D4">
+        <v>67.62424486398791</v>
+      </c>
+      <c r="E4">
+        <v>-47.004</v>
+      </c>
+      <c r="F4">
+        <v>1.696</v>
+      </c>
+      <c r="G4">
+        <v>11.6</v>
+      </c>
+      <c r="H4">
+        <v>36.1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>10.1</v>
+      </c>
+      <c r="K4">
+        <v>3.14</v>
+      </c>
+      <c r="L4">
+        <v>6.96</v>
+      </c>
+      <c r="M4">
+        <v>0.07750720000000001</v>
+      </c>
+      <c r="N4">
+        <v>6.8824928</v>
+      </c>
+      <c r="O4">
+        <v>2.030335376</v>
+      </c>
+      <c r="P4">
+        <v>4.852157424</v>
+      </c>
+      <c r="Q4">
+        <v>7.992157423999999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1315305919848467</v>
+      </c>
+      <c r="T4">
+        <v>1.06917330332712</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W4">
+        <v>0.0322185</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>89.79810907889846</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1292088599198926</v>
+      </c>
+      <c r="C5">
+        <v>76.9311856806553</v>
+      </c>
+      <c r="D5">
+        <v>67.87518568065531</v>
+      </c>
+      <c r="E5">
+        <v>-46.15600000000001</v>
+      </c>
+      <c r="F5">
+        <v>2.544</v>
+      </c>
+      <c r="G5">
+        <v>11.6</v>
+      </c>
+      <c r="H5">
+        <v>36.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>10.1</v>
+      </c>
+      <c r="K5">
+        <v>3.14</v>
+      </c>
+      <c r="L5">
+        <v>6.96</v>
+      </c>
+      <c r="M5">
+        <v>0.1162608</v>
+      </c>
+      <c r="N5">
+        <v>6.8437392</v>
+      </c>
+      <c r="O5">
+        <v>2.018903063999999</v>
+      </c>
+      <c r="P5">
+        <v>4.824836136</v>
+      </c>
+      <c r="Q5">
+        <v>7.964836136</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1322085617730852</v>
+      </c>
+      <c r="T5">
+        <v>1.076990218786533</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.0322185</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>59.86540605259898</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1288733696946354</v>
+      </c>
+      <c r="C6">
+        <v>76.33599582210532</v>
+      </c>
+      <c r="D6">
+        <v>68.12799582210532</v>
+      </c>
+      <c r="E6">
+        <v>-45.308</v>
+      </c>
+      <c r="F6">
+        <v>3.392</v>
+      </c>
+      <c r="G6">
+        <v>11.6</v>
+      </c>
+      <c r="H6">
+        <v>36.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>10.1</v>
+      </c>
+      <c r="K6">
+        <v>3.14</v>
+      </c>
+      <c r="L6">
+        <v>6.96</v>
+      </c>
+      <c r="M6">
+        <v>0.1550144</v>
+      </c>
+      <c r="N6">
+        <v>6.8049856</v>
+      </c>
+      <c r="O6">
+        <v>2.007470752</v>
+      </c>
+      <c r="P6">
+        <v>4.797514848</v>
+      </c>
+      <c r="Q6">
+        <v>7.937514848</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1329006559319118</v>
+      </c>
+      <c r="T6">
+        <v>1.08496998665135</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.0322185</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>44.89905453944923</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1285378794693782</v>
+      </c>
+      <c r="C7">
+        <v>75.74269625407261</v>
+      </c>
+      <c r="D7">
+        <v>68.38269625407261</v>
+      </c>
+      <c r="E7">
+        <v>-44.46</v>
+      </c>
+      <c r="F7">
+        <v>4.240000000000001</v>
+      </c>
+      <c r="G7">
+        <v>11.6</v>
+      </c>
+      <c r="H7">
+        <v>36.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>10.1</v>
+      </c>
+      <c r="K7">
+        <v>3.14</v>
+      </c>
+      <c r="L7">
+        <v>6.96</v>
+      </c>
+      <c r="M7">
+        <v>0.1937680000000001</v>
+      </c>
+      <c r="N7">
+        <v>6.766232</v>
+      </c>
+      <c r="O7">
+        <v>1.996038439999999</v>
+      </c>
+      <c r="P7">
+        <v>4.77019356</v>
+      </c>
+      <c r="Q7">
+        <v>7.91019356</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1336073204940823</v>
+      </c>
+      <c r="T7">
+        <v>1.093117749629111</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.0322185</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>35.91924363155938</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1282023892441209</v>
+      </c>
+      <c r="C8">
+        <v>75.15130825699495</v>
+      </c>
+      <c r="D8">
+        <v>68.63930825699495</v>
+      </c>
+      <c r="E8">
+        <v>-43.612</v>
+      </c>
+      <c r="F8">
+        <v>5.088</v>
+      </c>
+      <c r="G8">
+        <v>11.6</v>
+      </c>
+      <c r="H8">
+        <v>36.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>10.1</v>
+      </c>
+      <c r="K8">
+        <v>3.14</v>
+      </c>
+      <c r="L8">
+        <v>6.96</v>
+      </c>
+      <c r="M8">
+        <v>0.2325216</v>
+      </c>
+      <c r="N8">
+        <v>6.7274784</v>
+      </c>
+      <c r="O8">
+        <v>1.984606128</v>
+      </c>
+      <c r="P8">
+        <v>4.742872272</v>
+      </c>
+      <c r="Q8">
+        <v>7.882872272</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1343290204724691</v>
+      </c>
+      <c r="T8">
+        <v>1.101438869265973</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.0322185</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>29.93270302629949</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1278668990188637</v>
+      </c>
+      <c r="C9">
+        <v>74.56185343193992</v>
+      </c>
+      <c r="D9">
+        <v>68.89785343193994</v>
+      </c>
+      <c r="E9">
+        <v>-42.764</v>
+      </c>
+      <c r="F9">
+        <v>5.936000000000002</v>
+      </c>
+      <c r="G9">
+        <v>11.6</v>
+      </c>
+      <c r="H9">
+        <v>36.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>10.1</v>
+      </c>
+      <c r="K9">
+        <v>3.14</v>
+      </c>
+      <c r="L9">
+        <v>6.96</v>
+      </c>
+      <c r="M9">
+        <v>0.2712752000000001</v>
+      </c>
+      <c r="N9">
+        <v>6.6887248</v>
+      </c>
+      <c r="O9">
+        <v>1.973173816</v>
+      </c>
+      <c r="P9">
+        <v>4.715550984</v>
+      </c>
+      <c r="Q9">
+        <v>7.855550984</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1350662408804986</v>
+      </c>
+      <c r="T9">
+        <v>1.10993893771223</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.0322185</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>25.65660259397098</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1275314087936066</v>
+      </c>
+      <c r="C10">
+        <v>73.97435370666655</v>
+      </c>
+      <c r="D10">
+        <v>69.15835370666656</v>
+      </c>
+      <c r="E10">
+        <v>-41.916</v>
+      </c>
+      <c r="F10">
+        <v>6.784000000000001</v>
+      </c>
+      <c r="G10">
+        <v>11.6</v>
+      </c>
+      <c r="H10">
+        <v>36.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>10.1</v>
+      </c>
+      <c r="K10">
+        <v>3.14</v>
+      </c>
+      <c r="L10">
+        <v>6.96</v>
+      </c>
+      <c r="M10">
+        <v>0.3100288</v>
+      </c>
+      <c r="N10">
+        <v>6.6499712</v>
+      </c>
+      <c r="O10">
+        <v>1.961741503999999</v>
+      </c>
+      <c r="P10">
+        <v>4.688229696000001</v>
+      </c>
+      <c r="Q10">
+        <v>7.828229696</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1358194878191376</v>
+      </c>
+      <c r="T10">
+        <v>1.118623790255145</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.0322185</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>22.44952726972462</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1271959185683493</v>
+      </c>
+      <c r="C11">
+        <v>73.38883134182488</v>
+      </c>
+      <c r="D11">
+        <v>69.42083134182489</v>
+      </c>
+      <c r="E11">
+        <v>-41.068</v>
+      </c>
+      <c r="F11">
+        <v>7.632000000000001</v>
+      </c>
+      <c r="G11">
+        <v>11.6</v>
+      </c>
+      <c r="H11">
+        <v>36.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>10.1</v>
+      </c>
+      <c r="K11">
+        <v>3.14</v>
+      </c>
+      <c r="L11">
+        <v>6.96</v>
+      </c>
+      <c r="M11">
+        <v>0.3487824</v>
+      </c>
+      <c r="N11">
+        <v>6.6112176</v>
+      </c>
+      <c r="O11">
+        <v>1.950309192</v>
+      </c>
+      <c r="P11">
+        <v>4.660908408</v>
+      </c>
+      <c r="Q11">
+        <v>7.800908408</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1365892896355487</v>
+      </c>
+      <c r="T11">
+        <v>1.127499518678124</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W11">
+        <v>0.0322185</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>19.95513535086632</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1268604283430921</v>
+      </c>
+      <c r="C12">
+        <v>72.80530893729683</v>
+      </c>
+      <c r="D12">
+        <v>69.68530893729684</v>
+      </c>
+      <c r="E12">
+        <v>-40.22</v>
+      </c>
+      <c r="F12">
+        <v>8.480000000000002</v>
+      </c>
+      <c r="G12">
+        <v>11.6</v>
+      </c>
+      <c r="H12">
+        <v>36.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>10.1</v>
+      </c>
+      <c r="K12">
+        <v>3.14</v>
+      </c>
+      <c r="L12">
+        <v>6.96</v>
+      </c>
+      <c r="M12">
+        <v>0.3875360000000002</v>
+      </c>
+      <c r="N12">
+        <v>6.572464</v>
+      </c>
+      <c r="O12">
+        <v>1.93887688</v>
+      </c>
+      <c r="P12">
+        <v>4.633587120000001</v>
+      </c>
+      <c r="Q12">
+        <v>7.77358712</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1373761981589912</v>
+      </c>
+      <c r="T12">
+        <v>1.136572485510502</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W12">
+        <v>0.0322185</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>17.95962181577969</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1265249381178349</v>
+      </c>
+      <c r="C13">
+        <v>72.22380943868322</v>
+      </c>
+      <c r="D13">
+        <v>69.95180943868323</v>
+      </c>
+      <c r="E13">
+        <v>-39.372</v>
+      </c>
+      <c r="F13">
+        <v>9.328000000000001</v>
+      </c>
+      <c r="G13">
+        <v>11.6</v>
+      </c>
+      <c r="H13">
+        <v>36.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>10.1</v>
+      </c>
+      <c r="K13">
+        <v>3.14</v>
+      </c>
+      <c r="L13">
+        <v>6.96</v>
+      </c>
+      <c r="M13">
+        <v>0.4262896000000001</v>
+      </c>
+      <c r="N13">
+        <v>6.533710399999999</v>
+      </c>
+      <c r="O13">
+        <v>1.927444567999999</v>
+      </c>
+      <c r="P13">
+        <v>4.606265832</v>
+      </c>
+      <c r="Q13">
+        <v>7.746265832</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1381807900200392</v>
+      </c>
+      <c r="T13">
+        <v>1.14584933923799</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W13">
+        <v>0.0322185</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>16.32692892343608</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1261894478925777</v>
+      </c>
+      <c r="C14">
+        <v>71.64435614393967</v>
+      </c>
+      <c r="D14">
+        <v>70.22035614393968</v>
+      </c>
+      <c r="E14">
+        <v>-38.524</v>
+      </c>
+      <c r="F14">
+        <v>10.176</v>
+      </c>
+      <c r="G14">
+        <v>11.6</v>
+      </c>
+      <c r="H14">
+        <v>36.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>10.1</v>
+      </c>
+      <c r="K14">
+        <v>3.14</v>
+      </c>
+      <c r="L14">
+        <v>6.96</v>
+      </c>
+      <c r="M14">
+        <v>0.4650432</v>
+      </c>
+      <c r="N14">
+        <v>6.4949568</v>
+      </c>
+      <c r="O14">
+        <v>1.916012255999999</v>
+      </c>
+      <c r="P14">
+        <v>4.578944544000001</v>
+      </c>
+      <c r="Q14">
+        <v>7.718944544</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1390036680597474</v>
+      </c>
+      <c r="T14">
+        <v>1.155337030550194</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.0322185</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>14.96635151314974</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1258539576673205</v>
+      </c>
+      <c r="C15">
+        <v>71.06697271016635</v>
+      </c>
+      <c r="D15">
+        <v>70.49097271016636</v>
+      </c>
+      <c r="E15">
+        <v>-37.676</v>
+      </c>
+      <c r="F15">
+        <v>11.024</v>
+      </c>
+      <c r="G15">
+        <v>11.6</v>
+      </c>
+      <c r="H15">
+        <v>36.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>10.1</v>
+      </c>
+      <c r="K15">
+        <v>3.14</v>
+      </c>
+      <c r="L15">
+        <v>6.96</v>
+      </c>
+      <c r="M15">
+        <v>0.5037968000000002</v>
+      </c>
+      <c r="N15">
+        <v>6.4562032</v>
+      </c>
+      <c r="O15">
+        <v>1.904579944</v>
+      </c>
+      <c r="P15">
+        <v>4.551623256000001</v>
+      </c>
+      <c r="Q15">
+        <v>7.691623256000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1398454628360006</v>
+      </c>
+      <c r="T15">
+        <v>1.165042829708655</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W15">
+        <v>0.0322185</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>13.81509370444592</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1256763874420633</v>
+      </c>
+      <c r="C16">
+        <v>70.36305211161581</v>
+      </c>
+      <c r="D16">
+        <v>70.63505211161582</v>
+      </c>
+      <c r="E16">
+        <v>-36.828</v>
+      </c>
+      <c r="F16">
+        <v>11.872</v>
+      </c>
+      <c r="G16">
+        <v>11.6</v>
+      </c>
+      <c r="H16">
+        <v>36.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>10.1</v>
+      </c>
+      <c r="K16">
+        <v>3.14</v>
+      </c>
+      <c r="L16">
+        <v>6.96</v>
+      </c>
+      <c r="M16">
+        <v>0.5615456000000002</v>
+      </c>
+      <c r="N16">
+        <v>6.398454399999999</v>
+      </c>
+      <c r="O16">
+        <v>1.887544047999999</v>
+      </c>
+      <c r="P16">
+        <v>4.510910352</v>
+      </c>
+      <c r="Q16">
+        <v>7.650910351999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1407068342349573</v>
+      </c>
+      <c r="T16">
+        <v>1.174974345126615</v>
+      </c>
+      <c r="U16">
+        <v>0.0473</v>
+      </c>
+      <c r="V16">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W16">
+        <v>0.0333465</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>12.39436298672805</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1253521772168061</v>
+      </c>
+      <c r="C17">
+        <v>69.77963940326531</v>
+      </c>
+      <c r="D17">
+        <v>70.89963940326531</v>
+      </c>
+      <c r="E17">
+        <v>-35.98</v>
+      </c>
+      <c r="F17">
+        <v>12.72</v>
+      </c>
+      <c r="G17">
+        <v>11.6</v>
+      </c>
+      <c r="H17">
+        <v>36.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>10.1</v>
+      </c>
+      <c r="K17">
+        <v>3.14</v>
+      </c>
+      <c r="L17">
+        <v>6.96</v>
+      </c>
+      <c r="M17">
+        <v>0.6016560000000001</v>
+      </c>
+      <c r="N17">
+        <v>6.358344</v>
+      </c>
+      <c r="O17">
+        <v>1.875711479999999</v>
+      </c>
+      <c r="P17">
+        <v>4.48263252</v>
+      </c>
+      <c r="Q17">
+        <v>7.62263252</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1415884731962425</v>
+      </c>
+      <c r="T17">
+        <v>1.185139543260292</v>
+      </c>
+      <c r="U17">
+        <v>0.0473</v>
+      </c>
+      <c r="V17">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W17">
+        <v>0.0333465</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>11.56807212094619</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1250279669915489</v>
+      </c>
+      <c r="C18">
+        <v>69.19821634881524</v>
+      </c>
+      <c r="D18">
+        <v>71.16621634881524</v>
+      </c>
+      <c r="E18">
+        <v>-35.13200000000001</v>
+      </c>
+      <c r="F18">
+        <v>13.568</v>
+      </c>
+      <c r="G18">
+        <v>11.6</v>
+      </c>
+      <c r="H18">
+        <v>36.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>10.1</v>
+      </c>
+      <c r="K18">
+        <v>3.14</v>
+      </c>
+      <c r="L18">
+        <v>6.96</v>
+      </c>
+      <c r="M18">
+        <v>0.6417664000000001</v>
+      </c>
+      <c r="N18">
+        <v>6.3182336</v>
+      </c>
+      <c r="O18">
+        <v>1.863878912</v>
+      </c>
+      <c r="P18">
+        <v>4.454354688</v>
+      </c>
+      <c r="Q18">
+        <v>7.594354688</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1424911035613677</v>
+      </c>
+      <c r="T18">
+        <v>1.195546769920961</v>
+      </c>
+      <c r="U18">
+        <v>0.0473</v>
+      </c>
+      <c r="V18">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W18">
+        <v>0.0333465</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>10.84506761338705</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1251591867662917</v>
+      </c>
+      <c r="C19">
+        <v>68.24208176315892</v>
+      </c>
+      <c r="D19">
+        <v>71.05808176315892</v>
+      </c>
+      <c r="E19">
+        <v>-34.284</v>
+      </c>
+      <c r="F19">
+        <v>14.416</v>
+      </c>
+      <c r="G19">
+        <v>11.6</v>
+      </c>
+      <c r="H19">
+        <v>36.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>10.1</v>
+      </c>
+      <c r="K19">
+        <v>3.14</v>
+      </c>
+      <c r="L19">
+        <v>6.96</v>
+      </c>
+      <c r="M19">
+        <v>0.7366576000000001</v>
+      </c>
+      <c r="N19">
+        <v>6.2233424</v>
+      </c>
+      <c r="O19">
+        <v>1.835886007999999</v>
+      </c>
+      <c r="P19">
+        <v>4.387456392000001</v>
+      </c>
+      <c r="Q19">
+        <v>7.527456392</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1434154840557731</v>
+      </c>
+      <c r="T19">
+        <v>1.20620477312767</v>
+      </c>
+      <c r="U19">
+        <v>0.0511</v>
+      </c>
+      <c r="V19">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W19">
+        <v>0.0360255</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>9.448080084967559</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1248617665410344</v>
+      </c>
+      <c r="C20">
+        <v>67.63965086467473</v>
+      </c>
+      <c r="D20">
+        <v>71.30365086467474</v>
+      </c>
+      <c r="E20">
+        <v>-33.436</v>
+      </c>
+      <c r="F20">
+        <v>15.264</v>
+      </c>
+      <c r="G20">
+        <v>11.6</v>
+      </c>
+      <c r="H20">
+        <v>36.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>10.1</v>
+      </c>
+      <c r="K20">
+        <v>3.14</v>
+      </c>
+      <c r="L20">
+        <v>6.96</v>
+      </c>
+      <c r="M20">
+        <v>0.7799904000000001</v>
+      </c>
+      <c r="N20">
+        <v>6.1800096</v>
+      </c>
+      <c r="O20">
+        <v>1.823102832</v>
+      </c>
+      <c r="P20">
+        <v>4.356906768</v>
+      </c>
+      <c r="Q20">
+        <v>7.496906768</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1443624104158956</v>
+      </c>
+      <c r="T20">
+        <v>1.217122727632104</v>
+      </c>
+      <c r="U20">
+        <v>0.0511</v>
+      </c>
+      <c r="V20">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W20">
+        <v>0.0360255</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.923186746913807</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1245643463157772</v>
+      </c>
+      <c r="C21">
+        <v>67.03892317319031</v>
+      </c>
+      <c r="D21">
+        <v>71.55092317319033</v>
+      </c>
+      <c r="E21">
+        <v>-32.588</v>
+      </c>
+      <c r="F21">
+        <v>16.112</v>
+      </c>
+      <c r="G21">
+        <v>11.6</v>
+      </c>
+      <c r="H21">
+        <v>36.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>10.1</v>
+      </c>
+      <c r="K21">
+        <v>3.14</v>
+      </c>
+      <c r="L21">
+        <v>6.96</v>
+      </c>
+      <c r="M21">
+        <v>0.8233232000000001</v>
+      </c>
+      <c r="N21">
+        <v>6.1366768</v>
+      </c>
+      <c r="O21">
+        <v>1.810319656</v>
+      </c>
+      <c r="P21">
+        <v>4.326357144</v>
+      </c>
+      <c r="Q21">
+        <v>7.466357144</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.145332717673799</v>
+      </c>
+      <c r="T21">
+        <v>1.228310261260105</v>
+      </c>
+      <c r="U21">
+        <v>0.0511</v>
+      </c>
+      <c r="V21">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W21">
+        <v>0.0360255</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.453545339181503</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.12426692609052</v>
+      </c>
+      <c r="C22">
+        <v>66.43991646990713</v>
+      </c>
+      <c r="D22">
+        <v>71.79991646990715</v>
+      </c>
+      <c r="E22">
+        <v>-31.74</v>
+      </c>
+      <c r="F22">
+        <v>16.96</v>
+      </c>
+      <c r="G22">
+        <v>11.6</v>
+      </c>
+      <c r="H22">
+        <v>36.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>10.1</v>
+      </c>
+      <c r="K22">
+        <v>3.14</v>
+      </c>
+      <c r="L22">
+        <v>6.96</v>
+      </c>
+      <c r="M22">
+        <v>0.8666560000000002</v>
+      </c>
+      <c r="N22">
+        <v>6.093344</v>
+      </c>
+      <c r="O22">
+        <v>1.79753648</v>
+      </c>
+      <c r="P22">
+        <v>4.29580752</v>
+      </c>
+      <c r="Q22">
+        <v>7.43580752</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.14632728261315</v>
+      </c>
+      <c r="T22">
+        <v>1.239777483228805</v>
+      </c>
+      <c r="U22">
+        <v>0.0511</v>
+      </c>
+      <c r="V22">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W22">
+        <v>0.0360255</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>8.030868072222425</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1242508008652628</v>
+      </c>
+      <c r="C23">
+        <v>65.60546566798139</v>
+      </c>
+      <c r="D23">
+        <v>71.8134656679814</v>
+      </c>
+      <c r="E23">
+        <v>-30.892</v>
+      </c>
+      <c r="F23">
+        <v>17.808</v>
+      </c>
+      <c r="G23">
+        <v>11.6</v>
+      </c>
+      <c r="H23">
+        <v>36.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>10.1</v>
+      </c>
+      <c r="K23">
+        <v>3.14</v>
+      </c>
+      <c r="L23">
+        <v>6.96</v>
+      </c>
+      <c r="M23">
+        <v>0.9438240000000003</v>
+      </c>
+      <c r="N23">
+        <v>6.016176</v>
+      </c>
+      <c r="O23">
+        <v>1.774771919999999</v>
+      </c>
+      <c r="P23">
+        <v>4.241404080000001</v>
+      </c>
+      <c r="Q23">
+        <v>7.38140408</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1473470264117251</v>
+      </c>
+      <c r="T23">
+        <v>1.251535014614434</v>
+      </c>
+      <c r="U23">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W23">
+        <v>0.03736500000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.374256217260843</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1239667756400056</v>
+      </c>
+      <c r="C24">
+        <v>64.99695854075451</v>
+      </c>
+      <c r="D24">
+        <v>72.05295854075452</v>
+      </c>
+      <c r="E24">
+        <v>-30.044</v>
+      </c>
+      <c r="F24">
+        <v>18.656</v>
+      </c>
+      <c r="G24">
+        <v>11.6</v>
+      </c>
+      <c r="H24">
+        <v>36.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>10.1</v>
+      </c>
+      <c r="K24">
+        <v>3.14</v>
+      </c>
+      <c r="L24">
+        <v>6.96</v>
+      </c>
+      <c r="M24">
+        <v>0.9887680000000002</v>
+      </c>
+      <c r="N24">
+        <v>5.971232</v>
+      </c>
+      <c r="O24">
+        <v>1.761513439999999</v>
+      </c>
+      <c r="P24">
+        <v>4.209718560000001</v>
+      </c>
+      <c r="Q24">
+        <v>7.34971856</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1483929174871867</v>
+      </c>
+      <c r="T24">
+        <v>1.263594021163798</v>
+      </c>
+      <c r="U24">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W24">
+        <v>0.03736500000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>7.039062752839897</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1236827504147484</v>
+      </c>
+      <c r="C25">
+        <v>64.39005414239315</v>
+      </c>
+      <c r="D25">
+        <v>72.29405414239316</v>
+      </c>
+      <c r="E25">
+        <v>-29.196</v>
+      </c>
+      <c r="F25">
+        <v>19.504</v>
+      </c>
+      <c r="G25">
+        <v>11.6</v>
+      </c>
+      <c r="H25">
+        <v>36.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>10.1</v>
+      </c>
+      <c r="K25">
+        <v>3.14</v>
+      </c>
+      <c r="L25">
+        <v>6.96</v>
+      </c>
+      <c r="M25">
+        <v>1.033712</v>
+      </c>
+      <c r="N25">
+        <v>5.926288</v>
+      </c>
+      <c r="O25">
+        <v>1.748254959999999</v>
+      </c>
+      <c r="P25">
+        <v>4.17803304</v>
+      </c>
+      <c r="Q25">
+        <v>7.31803304</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1494659745646083</v>
+      </c>
+      <c r="T25">
+        <v>1.275966248662496</v>
+      </c>
+      <c r="U25">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W25">
+        <v>0.03736500000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.733016546194682</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1233987251894912</v>
+      </c>
+      <c r="C26">
+        <v>63.78476861553156</v>
+      </c>
+      <c r="D26">
+        <v>72.53676861553157</v>
+      </c>
+      <c r="E26">
+        <v>-28.348</v>
+      </c>
+      <c r="F26">
+        <v>20.352</v>
+      </c>
+      <c r="G26">
+        <v>11.6</v>
+      </c>
+      <c r="H26">
+        <v>36.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>10.1</v>
+      </c>
+      <c r="K26">
+        <v>3.14</v>
+      </c>
+      <c r="L26">
+        <v>6.96</v>
+      </c>
+      <c r="M26">
+        <v>1.078656</v>
+      </c>
+      <c r="N26">
+        <v>5.881344</v>
+      </c>
+      <c r="O26">
+        <v>1.73499648</v>
+      </c>
+      <c r="P26">
+        <v>4.146347520000001</v>
+      </c>
+      <c r="Q26">
+        <v>7.286347520000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1505672699861726</v>
+      </c>
+      <c r="T26">
+        <v>1.28866406109537</v>
+      </c>
+      <c r="U26">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W26">
+        <v>0.03736500000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.452474190103239</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.123467199964234</v>
+      </c>
+      <c r="C27">
+        <v>62.87810435246847</v>
+      </c>
+      <c r="D27">
+        <v>72.47810435246848</v>
+      </c>
+      <c r="E27">
+        <v>-27.5</v>
+      </c>
+      <c r="F27">
+        <v>21.2</v>
+      </c>
+      <c r="G27">
+        <v>11.6</v>
+      </c>
+      <c r="H27">
+        <v>36.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>10.1</v>
+      </c>
+      <c r="K27">
+        <v>3.14</v>
+      </c>
+      <c r="L27">
+        <v>6.96</v>
+      </c>
+      <c r="M27">
+        <v>1.166</v>
+      </c>
+      <c r="N27">
+        <v>5.794</v>
+      </c>
+      <c r="O27">
+        <v>1.709229999999999</v>
+      </c>
+      <c r="P27">
+        <v>4.084770000000001</v>
+      </c>
+      <c r="Q27">
+        <v>7.22477</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1516979332856453</v>
+      </c>
+      <c r="T27">
+        <v>1.301700481859787</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.038775</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.969125214408233</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1231972747389768</v>
+      </c>
+      <c r="C28">
+        <v>62.26190885923793</v>
+      </c>
+      <c r="D28">
+        <v>72.70990885923794</v>
+      </c>
+      <c r="E28">
+        <v>-26.652</v>
+      </c>
+      <c r="F28">
+        <v>22.04800000000001</v>
+      </c>
+      <c r="G28">
+        <v>11.6</v>
+      </c>
+      <c r="H28">
+        <v>36.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>10.1</v>
+      </c>
+      <c r="K28">
+        <v>3.14</v>
+      </c>
+      <c r="L28">
+        <v>6.96</v>
+      </c>
+      <c r="M28">
+        <v>1.21264</v>
+      </c>
+      <c r="N28">
+        <v>5.74736</v>
+      </c>
+      <c r="O28">
+        <v>1.695471199999999</v>
+      </c>
+      <c r="P28">
+        <v>4.0518888</v>
+      </c>
+      <c r="Q28">
+        <v>7.1918888</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1528591550526713</v>
+      </c>
+      <c r="T28">
+        <v>1.31508923832054</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W28">
+        <v>0.038775</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.73954347539253</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1229273495137196</v>
+      </c>
+      <c r="C29">
+        <v>61.64720086998958</v>
+      </c>
+      <c r="D29">
+        <v>72.94320086998958</v>
+      </c>
+      <c r="E29">
+        <v>-25.804</v>
+      </c>
+      <c r="F29">
+        <v>22.896</v>
+      </c>
+      <c r="G29">
+        <v>11.6</v>
+      </c>
+      <c r="H29">
+        <v>36.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>10.1</v>
+      </c>
+      <c r="K29">
+        <v>3.14</v>
+      </c>
+      <c r="L29">
+        <v>6.96</v>
+      </c>
+      <c r="M29">
+        <v>1.25928</v>
+      </c>
+      <c r="N29">
+        <v>5.70072</v>
+      </c>
+      <c r="O29">
+        <v>1.681712399999999</v>
+      </c>
+      <c r="P29">
+        <v>4.0190076</v>
+      </c>
+      <c r="Q29">
+        <v>7.1590076</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1540521911146843</v>
+      </c>
+      <c r="T29">
+        <v>1.328844810026792</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.038775</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.526967791118733</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1226574242884623</v>
+      </c>
+      <c r="C30">
+        <v>61.03399474892014</v>
+      </c>
+      <c r="D30">
+        <v>73.17799474892016</v>
+      </c>
+      <c r="E30">
+        <v>-24.956</v>
+      </c>
+      <c r="F30">
+        <v>23.74400000000001</v>
+      </c>
+      <c r="G30">
+        <v>11.6</v>
+      </c>
+      <c r="H30">
+        <v>36.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>10.1</v>
+      </c>
+      <c r="K30">
+        <v>3.14</v>
+      </c>
+      <c r="L30">
+        <v>6.96</v>
+      </c>
+      <c r="M30">
+        <v>1.30592</v>
+      </c>
+      <c r="N30">
+        <v>5.65408</v>
+      </c>
+      <c r="O30">
+        <v>1.667953599999999</v>
+      </c>
+      <c r="P30">
+        <v>3.9861264</v>
+      </c>
+      <c r="Q30">
+        <v>7.1261264</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1552783670673088</v>
+      </c>
+      <c r="T30">
+        <v>1.342982480947108</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W30">
+        <v>0.038775</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.329576084293064</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1223874990632051</v>
+      </c>
+      <c r="C31">
+        <v>60.42230504576891</v>
+      </c>
+      <c r="D31">
+        <v>73.41430504576891</v>
+      </c>
+      <c r="E31">
+        <v>-24.108</v>
+      </c>
+      <c r="F31">
+        <v>24.592</v>
+      </c>
+      <c r="G31">
+        <v>11.6</v>
+      </c>
+      <c r="H31">
+        <v>36.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>10.1</v>
+      </c>
+      <c r="K31">
+        <v>3.14</v>
+      </c>
+      <c r="L31">
+        <v>6.96</v>
+      </c>
+      <c r="M31">
+        <v>1.35256</v>
+      </c>
+      <c r="N31">
+        <v>5.60744</v>
+      </c>
+      <c r="O31">
+        <v>1.6541948</v>
+      </c>
+      <c r="P31">
+        <v>3.9532452</v>
+      </c>
+      <c r="Q31">
+        <v>7.0932452</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1565390831876129</v>
+      </c>
+      <c r="T31">
+        <v>1.3575183961187</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W31">
+        <v>0.038775</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.145797598627786</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1221175738379479</v>
+      </c>
+      <c r="C32">
+        <v>59.81214649882328</v>
+      </c>
+      <c r="D32">
+        <v>73.65214649882329</v>
+      </c>
+      <c r="E32">
+        <v>-23.26</v>
+      </c>
+      <c r="F32">
+        <v>25.44</v>
+      </c>
+      <c r="G32">
+        <v>11.6</v>
+      </c>
+      <c r="H32">
+        <v>36.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>10.1</v>
+      </c>
+      <c r="K32">
+        <v>3.14</v>
+      </c>
+      <c r="L32">
+        <v>6.96</v>
+      </c>
+      <c r="M32">
+        <v>1.3992</v>
+      </c>
+      <c r="N32">
+        <v>5.5608</v>
+      </c>
+      <c r="O32">
+        <v>1.640436</v>
+      </c>
+      <c r="P32">
+        <v>3.920364000000001</v>
+      </c>
+      <c r="Q32">
+        <v>7.060364</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.157835819768497</v>
+      </c>
+      <c r="T32">
+        <v>1.372469623152337</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W32">
+        <v>0.038775</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.974271012006861</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1218476486126907</v>
+      </c>
+      <c r="C33">
+        <v>59.20353403798274</v>
+      </c>
+      <c r="D33">
+        <v>73.89153403798275</v>
+      </c>
+      <c r="E33">
+        <v>-22.412</v>
+      </c>
+      <c r="F33">
+        <v>26.288</v>
+      </c>
+      <c r="G33">
+        <v>11.6</v>
+      </c>
+      <c r="H33">
+        <v>36.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>10.1</v>
+      </c>
+      <c r="K33">
+        <v>3.14</v>
+      </c>
+      <c r="L33">
+        <v>6.96</v>
+      </c>
+      <c r="M33">
+        <v>1.44584</v>
+      </c>
+      <c r="N33">
+        <v>5.51416</v>
+      </c>
+      <c r="O33">
+        <v>1.626677199999999</v>
+      </c>
+      <c r="P33">
+        <v>3.8874828</v>
+      </c>
+      <c r="Q33">
+        <v>7.0274828</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1591701429169431</v>
+      </c>
+      <c r="T33">
+        <v>1.387854219085501</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W33">
+        <v>0.038775</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.813810656780833</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1215777233874335</v>
+      </c>
+      <c r="C34">
+        <v>58.59648278788313</v>
+      </c>
+      <c r="D34">
+        <v>74.13248278788313</v>
+      </c>
+      <c r="E34">
+        <v>-21.564</v>
+      </c>
+      <c r="F34">
+        <v>27.136</v>
+      </c>
+      <c r="G34">
+        <v>11.6</v>
+      </c>
+      <c r="H34">
+        <v>36.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>10.1</v>
+      </c>
+      <c r="K34">
+        <v>3.14</v>
+      </c>
+      <c r="L34">
+        <v>6.96</v>
+      </c>
+      <c r="M34">
+        <v>1.49248</v>
+      </c>
+      <c r="N34">
+        <v>5.467519999999999</v>
+      </c>
+      <c r="O34">
+        <v>1.612918399999999</v>
+      </c>
+      <c r="P34">
+        <v>3.8546016</v>
+      </c>
+      <c r="Q34">
+        <v>6.994601599999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1605437108638728</v>
+      </c>
+      <c r="T34">
+        <v>1.403691303134345</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W34">
+        <v>0.038775</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.663379073756431</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1213077981621763</v>
+      </c>
+      <c r="C35">
+        <v>57.99100807108198</v>
+      </c>
+      <c r="D35">
+        <v>74.37500807108199</v>
+      </c>
+      <c r="E35">
+        <v>-20.716</v>
+      </c>
+      <c r="F35">
+        <v>27.98400000000001</v>
+      </c>
+      <c r="G35">
+        <v>11.6</v>
+      </c>
+      <c r="H35">
+        <v>36.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>10.1</v>
+      </c>
+      <c r="K35">
+        <v>3.14</v>
+      </c>
+      <c r="L35">
+        <v>6.96</v>
+      </c>
+      <c r="M35">
+        <v>1.53912</v>
+      </c>
+      <c r="N35">
+        <v>5.420879999999999</v>
+      </c>
+      <c r="O35">
+        <v>1.599159599999999</v>
+      </c>
+      <c r="P35">
+        <v>3.8217204</v>
+      </c>
+      <c r="Q35">
+        <v>6.9617204</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1619582808390691</v>
+      </c>
+      <c r="T35">
+        <v>1.420001135960767</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W35">
+        <v>0.038775</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.522064556369873</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1219487329369191</v>
+      </c>
+      <c r="C36">
+        <v>56.56970373605746</v>
+      </c>
+      <c r="D36">
+        <v>73.80170373605748</v>
+      </c>
+      <c r="E36">
+        <v>-19.868</v>
+      </c>
+      <c r="F36">
+        <v>28.832</v>
+      </c>
+      <c r="G36">
+        <v>11.6</v>
+      </c>
+      <c r="H36">
+        <v>36.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>10.1</v>
+      </c>
+      <c r="K36">
+        <v>3.14</v>
+      </c>
+      <c r="L36">
+        <v>6.96</v>
+      </c>
+      <c r="M36">
+        <v>1.6953216</v>
+      </c>
+      <c r="N36">
+        <v>5.264678399999999</v>
+      </c>
+      <c r="O36">
+        <v>1.553080128</v>
+      </c>
+      <c r="P36">
+        <v>3.711598272</v>
+      </c>
+      <c r="Q36">
+        <v>6.851598271999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1634157165710895</v>
+      </c>
+      <c r="T36">
+        <v>1.436805206145565</v>
+      </c>
+      <c r="U36">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W36">
+        <v>0.041454</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.105415751206142</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1227419477116619</v>
+      </c>
+      <c r="C37">
+        <v>55.02430984181859</v>
+      </c>
+      <c r="D37">
+        <v>73.1043098418186</v>
+      </c>
+      <c r="E37">
+        <v>-19.02</v>
+      </c>
+      <c r="F37">
+        <v>29.68000000000001</v>
+      </c>
+      <c r="G37">
+        <v>11.6</v>
+      </c>
+      <c r="H37">
+        <v>36.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>10.1</v>
+      </c>
+      <c r="K37">
+        <v>3.14</v>
+      </c>
+      <c r="L37">
+        <v>6.96</v>
+      </c>
+      <c r="M37">
+        <v>1.86984</v>
+      </c>
+      <c r="N37">
+        <v>5.090159999999999</v>
+      </c>
+      <c r="O37">
+        <v>1.501597199999999</v>
+      </c>
+      <c r="P37">
+        <v>3.5885628</v>
+      </c>
+      <c r="Q37">
+        <v>6.7285628</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1649179964794798</v>
+      </c>
+      <c r="T37">
+        <v>1.454126324643742</v>
+      </c>
+      <c r="U37">
+        <v>0.063</v>
+      </c>
+      <c r="V37">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W37">
+        <v>0.044415</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.722243614426902</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1225284224864047</v>
+      </c>
+      <c r="C38">
+        <v>54.36274132783853</v>
+      </c>
+      <c r="D38">
+        <v>73.29074132783855</v>
+      </c>
+      <c r="E38">
+        <v>-18.172</v>
+      </c>
+      <c r="F38">
+        <v>30.528</v>
+      </c>
+      <c r="G38">
+        <v>11.6</v>
+      </c>
+      <c r="H38">
+        <v>36.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>10.1</v>
+      </c>
+      <c r="K38">
+        <v>3.14</v>
+      </c>
+      <c r="L38">
+        <v>6.96</v>
+      </c>
+      <c r="M38">
+        <v>1.923264</v>
+      </c>
+      <c r="N38">
+        <v>5.036735999999999</v>
+      </c>
+      <c r="O38">
+        <v>1.48583712</v>
+      </c>
+      <c r="P38">
+        <v>3.55089888</v>
+      </c>
+      <c r="Q38">
+        <v>6.69089888</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1664672226350073</v>
+      </c>
+      <c r="T38">
+        <v>1.471988728094987</v>
+      </c>
+      <c r="U38">
+        <v>0.063</v>
+      </c>
+      <c r="V38">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W38">
+        <v>0.044415</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.618847958470599</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1223148972611475</v>
+      </c>
+      <c r="C39">
+        <v>53.70212612461751</v>
+      </c>
+      <c r="D39">
+        <v>73.47812612461752</v>
+      </c>
+      <c r="E39">
+        <v>-17.324</v>
+      </c>
+      <c r="F39">
+        <v>31.376</v>
+      </c>
+      <c r="G39">
+        <v>11.6</v>
+      </c>
+      <c r="H39">
+        <v>36.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>10.1</v>
+      </c>
+      <c r="K39">
+        <v>3.14</v>
+      </c>
+      <c r="L39">
+        <v>6.96</v>
+      </c>
+      <c r="M39">
+        <v>1.976688</v>
+      </c>
+      <c r="N39">
+        <v>4.983312</v>
+      </c>
+      <c r="O39">
+        <v>1.47007704</v>
+      </c>
+      <c r="P39">
+        <v>3.51323496</v>
+      </c>
+      <c r="Q39">
+        <v>6.65323496</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1680656305732499</v>
+      </c>
+      <c r="T39">
+        <v>1.490418191973255</v>
+      </c>
+      <c r="U39">
+        <v>0.063</v>
+      </c>
+      <c r="V39">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W39">
+        <v>0.044415</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.521041256890313</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1240034620358902</v>
+      </c>
+      <c r="C40">
+        <v>51.39793440982692</v>
+      </c>
+      <c r="D40">
+        <v>72.02193440982693</v>
+      </c>
+      <c r="E40">
+        <v>-16.476</v>
+      </c>
+      <c r="F40">
+        <v>32.224</v>
+      </c>
+      <c r="G40">
+        <v>11.6</v>
+      </c>
+      <c r="H40">
+        <v>36.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>10.1</v>
+      </c>
+      <c r="K40">
+        <v>3.14</v>
+      </c>
+      <c r="L40">
+        <v>6.96</v>
+      </c>
+      <c r="M40">
+        <v>2.2589024</v>
+      </c>
+      <c r="N40">
+        <v>4.7010976</v>
+      </c>
+      <c r="O40">
+        <v>1.386823792</v>
+      </c>
+      <c r="P40">
+        <v>3.314273808</v>
+      </c>
+      <c r="Q40">
+        <v>6.454273808</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1697156000578875</v>
+      </c>
+      <c r="T40">
+        <v>1.509442154686306</v>
+      </c>
+      <c r="U40">
+        <v>0.0701</v>
+      </c>
+      <c r="V40">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W40">
+        <v>0.0494205</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.081142416777281</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.123839991810633</v>
+      </c>
+      <c r="C41">
+        <v>50.68838035262111</v>
+      </c>
+      <c r="D41">
+        <v>72.16038035262112</v>
+      </c>
+      <c r="E41">
+        <v>-15.628</v>
+      </c>
+      <c r="F41">
+        <v>33.072</v>
+      </c>
+      <c r="G41">
+        <v>11.6</v>
+      </c>
+      <c r="H41">
+        <v>36.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>10.1</v>
+      </c>
+      <c r="K41">
+        <v>3.14</v>
+      </c>
+      <c r="L41">
+        <v>6.96</v>
+      </c>
+      <c r="M41">
+        <v>2.3183472</v>
+      </c>
+      <c r="N41">
+        <v>4.6416528</v>
+      </c>
+      <c r="O41">
+        <v>1.369287576</v>
+      </c>
+      <c r="P41">
+        <v>3.272365224000001</v>
+      </c>
+      <c r="Q41">
+        <v>6.412365224</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1714196669026771</v>
+      </c>
+      <c r="T41">
+        <v>1.529089853881753</v>
+      </c>
+      <c r="U41">
+        <v>0.0701</v>
+      </c>
+      <c r="V41">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W41">
+        <v>0.0494205</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.002138765065043</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1296831215853758</v>
+      </c>
+      <c r="C42">
+        <v>45.20098791494967</v>
+      </c>
+      <c r="D42">
+        <v>67.52098791494969</v>
+      </c>
+      <c r="E42">
+        <v>-14.77999999999999</v>
+      </c>
+      <c r="F42">
+        <v>33.92000000000001</v>
+      </c>
+      <c r="G42">
+        <v>11.6</v>
+      </c>
+      <c r="H42">
+        <v>36.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>10.1</v>
+      </c>
+      <c r="K42">
+        <v>3.14</v>
+      </c>
+      <c r="L42">
+        <v>6.96</v>
+      </c>
+      <c r="M42">
+        <v>3.100288000000001</v>
+      </c>
+      <c r="N42">
+        <v>3.859711999999999</v>
+      </c>
+      <c r="O42">
+        <v>1.138615039999999</v>
+      </c>
+      <c r="P42">
+        <v>2.72109696</v>
+      </c>
+      <c r="Q42">
+        <v>5.861096959999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1731805359756264</v>
+      </c>
+      <c r="T42">
+        <v>1.549392476383714</v>
+      </c>
+      <c r="U42">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W42">
+        <v>0.06443700000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.244952726972461</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1296698163601186</v>
+      </c>
+      <c r="C43">
+        <v>44.36287438759576</v>
+      </c>
+      <c r="D43">
+        <v>67.53087438759577</v>
+      </c>
+      <c r="E43">
+        <v>-13.932</v>
+      </c>
+      <c r="F43">
+        <v>34.76800000000001</v>
+      </c>
+      <c r="G43">
+        <v>11.6</v>
+      </c>
+      <c r="H43">
+        <v>36.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>10.1</v>
+      </c>
+      <c r="K43">
+        <v>3.14</v>
+      </c>
+      <c r="L43">
+        <v>6.96</v>
+      </c>
+      <c r="M43">
+        <v>3.177795200000001</v>
+      </c>
+      <c r="N43">
+        <v>3.782204799999999</v>
+      </c>
+      <c r="O43">
+        <v>1.115750415999999</v>
+      </c>
+      <c r="P43">
+        <v>2.666454384</v>
+      </c>
+      <c r="Q43">
+        <v>5.806454383999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1750010955256248</v>
+      </c>
+      <c r="T43">
+        <v>1.570383323377267</v>
+      </c>
+      <c r="U43">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W43">
+        <v>0.06443700000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.190197782412157</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1296565111348614</v>
+      </c>
+      <c r="C44">
+        <v>43.52476375583496</v>
+      </c>
+      <c r="D44">
+        <v>67.54076375583497</v>
+      </c>
+      <c r="E44">
+        <v>-13.084</v>
+      </c>
+      <c r="F44">
+        <v>35.61600000000001</v>
+      </c>
+      <c r="G44">
+        <v>11.6</v>
+      </c>
+      <c r="H44">
+        <v>36.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>10.1</v>
+      </c>
+      <c r="K44">
+        <v>3.14</v>
+      </c>
+      <c r="L44">
+        <v>6.96</v>
+      </c>
+      <c r="M44">
+        <v>3.255302400000001</v>
+      </c>
+      <c r="N44">
+        <v>3.704697599999999</v>
+      </c>
+      <c r="O44">
+        <v>1.092885791999999</v>
+      </c>
+      <c r="P44">
+        <v>2.611811808</v>
+      </c>
+      <c r="Q44">
+        <v>5.751811807999999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1768844329911404</v>
+      </c>
+      <c r="T44">
+        <v>1.592097992680943</v>
+      </c>
+      <c r="U44">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W44">
+        <v>0.06443700000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.138050216164249</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1296432059096042</v>
+      </c>
+      <c r="C45">
+        <v>42.68665602093964</v>
+      </c>
+      <c r="D45">
+        <v>67.55065602093966</v>
+      </c>
+      <c r="E45">
+        <v>-12.236</v>
+      </c>
+      <c r="F45">
+        <v>36.46400000000001</v>
+      </c>
+      <c r="G45">
+        <v>11.6</v>
+      </c>
+      <c r="H45">
+        <v>36.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>10.1</v>
+      </c>
+      <c r="K45">
+        <v>3.14</v>
+      </c>
+      <c r="L45">
+        <v>6.96</v>
+      </c>
+      <c r="M45">
+        <v>3.332809600000001</v>
+      </c>
+      <c r="N45">
+        <v>3.627190399999999</v>
+      </c>
+      <c r="O45">
+        <v>1.070021167999999</v>
+      </c>
+      <c r="P45">
+        <v>2.557169232</v>
+      </c>
+      <c r="Q45">
+        <v>5.697169231999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1788338524729898</v>
+      </c>
+      <c r="T45">
+        <v>1.6145745802058</v>
+      </c>
+      <c r="U45">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W45">
+        <v>0.06443700000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.088328118113917</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.129629900684347</v>
+      </c>
+      <c r="C46">
+        <v>41.8485511841828</v>
+      </c>
+      <c r="D46">
+        <v>67.56055118418281</v>
+      </c>
+      <c r="E46">
+        <v>-11.388</v>
+      </c>
+      <c r="F46">
+        <v>37.312</v>
+      </c>
+      <c r="G46">
+        <v>11.6</v>
+      </c>
+      <c r="H46">
+        <v>36.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>10.1</v>
+      </c>
+      <c r="K46">
+        <v>3.14</v>
+      </c>
+      <c r="L46">
+        <v>6.96</v>
+      </c>
+      <c r="M46">
+        <v>3.410316800000001</v>
+      </c>
+      <c r="N46">
+        <v>3.549683199999999</v>
+      </c>
+      <c r="O46">
+        <v>1.047156543999999</v>
+      </c>
+      <c r="P46">
+        <v>2.502526656</v>
+      </c>
+      <c r="Q46">
+        <v>5.642526655999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1808528940791911</v>
+      </c>
+      <c r="T46">
+        <v>1.637853902999402</v>
+      </c>
+      <c r="U46">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W46">
+        <v>0.06443700000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.04086611542951</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1363105704590898</v>
+      </c>
+      <c r="C47">
+        <v>36.37182498418077</v>
+      </c>
+      <c r="D47">
+        <v>62.93182498418077</v>
+      </c>
+      <c r="E47">
+        <v>-10.54</v>
+      </c>
+      <c r="F47">
+        <v>38.16</v>
+      </c>
+      <c r="G47">
+        <v>11.6</v>
+      </c>
+      <c r="H47">
+        <v>36.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>10.1</v>
+      </c>
+      <c r="K47">
+        <v>3.14</v>
+      </c>
+      <c r="L47">
+        <v>6.96</v>
+      </c>
+      <c r="M47">
+        <v>4.293</v>
+      </c>
+      <c r="N47">
+        <v>2.667</v>
+      </c>
+      <c r="O47">
+        <v>0.7867649999999997</v>
+      </c>
+      <c r="P47">
+        <v>1.880235</v>
+      </c>
+      <c r="Q47">
+        <v>5.020235</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1829453553801632</v>
+      </c>
+      <c r="T47">
+        <v>1.661979746621862</v>
+      </c>
+      <c r="U47">
+        <v>0.1125</v>
+      </c>
+      <c r="V47">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W47">
+        <v>0.07931250000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>1.621243885394829</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1364460202338326</v>
+      </c>
+      <c r="C48">
+        <v>35.43652904013871</v>
+      </c>
+      <c r="D48">
+        <v>62.84452904013872</v>
+      </c>
+      <c r="E48">
+        <v>-9.691999999999993</v>
+      </c>
+      <c r="F48">
+        <v>39.00800000000001</v>
+      </c>
+      <c r="G48">
+        <v>11.6</v>
+      </c>
+      <c r="H48">
+        <v>36.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>10.1</v>
+      </c>
+      <c r="K48">
+        <v>3.14</v>
+      </c>
+      <c r="L48">
+        <v>6.96</v>
+      </c>
+      <c r="M48">
+        <v>4.388400000000002</v>
+      </c>
+      <c r="N48">
+        <v>2.571599999999998</v>
+      </c>
+      <c r="O48">
+        <v>0.7586219999999994</v>
+      </c>
+      <c r="P48">
+        <v>1.812977999999999</v>
+      </c>
+      <c r="Q48">
+        <v>4.952977999999998</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1851153152478381</v>
+      </c>
+      <c r="T48">
+        <v>1.686999140008118</v>
+      </c>
+      <c r="U48">
+        <v>0.1125</v>
+      </c>
+      <c r="V48">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W48">
+        <v>0.07931250000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>1.585999453103636</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1365814700085754</v>
+      </c>
+      <c r="C49">
+        <v>34.50147494592683</v>
+      </c>
+      <c r="D49">
+        <v>62.75747494592684</v>
+      </c>
+      <c r="E49">
+        <v>-8.843999999999994</v>
+      </c>
+      <c r="F49">
+        <v>39.85600000000001</v>
+      </c>
+      <c r="G49">
+        <v>11.6</v>
+      </c>
+      <c r="H49">
+        <v>36.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>10.1</v>
+      </c>
+      <c r="K49">
+        <v>3.14</v>
+      </c>
+      <c r="L49">
+        <v>6.96</v>
+      </c>
+      <c r="M49">
+        <v>4.483800000000001</v>
+      </c>
+      <c r="N49">
+        <v>2.476199999999999</v>
+      </c>
+      <c r="O49">
+        <v>0.7304789999999994</v>
+      </c>
+      <c r="P49">
+        <v>1.745720999999999</v>
+      </c>
+      <c r="Q49">
+        <v>4.885720999999998</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1873671603935384</v>
+      </c>
+      <c r="T49">
+        <v>1.712962661446685</v>
+      </c>
+      <c r="U49">
+        <v>0.1125</v>
+      </c>
+      <c r="V49">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W49">
+        <v>0.07931250000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>1.552254783888666</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1367169197833182</v>
+      </c>
+      <c r="C50">
+        <v>33.56666169788286</v>
+      </c>
+      <c r="D50">
+        <v>62.67066169788286</v>
+      </c>
+      <c r="E50">
+        <v>-7.996000000000002</v>
+      </c>
+      <c r="F50">
+        <v>40.704</v>
+      </c>
+      <c r="G50">
+        <v>11.6</v>
+      </c>
+      <c r="H50">
+        <v>36.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>10.1</v>
+      </c>
+      <c r="K50">
+        <v>3.14</v>
+      </c>
+      <c r="L50">
+        <v>6.96</v>
+      </c>
+      <c r="M50">
+        <v>4.5792</v>
+      </c>
+      <c r="N50">
+        <v>2.3808</v>
+      </c>
+      <c r="O50">
+        <v>0.7023359999999997</v>
+      </c>
+      <c r="P50">
+        <v>1.678464</v>
+      </c>
+      <c r="Q50">
+        <v>4.818464</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1897056149679195</v>
+      </c>
+      <c r="T50">
+        <v>1.739924779863658</v>
+      </c>
+      <c r="U50">
+        <v>0.1125</v>
+      </c>
+      <c r="V50">
+        <v>0.2949999999999999</v>
+      </c>
+      <c r="W50">
+        <v>0.07931250000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>1.519916142557652</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1720668155198579</v>
+      </c>
+      <c r="C51">
+        <v>16.09485817921918</v>
+      </c>
+      <c r="D51">
+        <v>46.04685817921919</v>
+      </c>
+      <c r="E51">
+        <v>-7.147999999999996</v>
+      </c>
+      <c r="F51">
+        <v>41.55200000000001</v>
+      </c>
+      <c r="G51">
+        <v>11.6</v>
+      </c>
+      <c r="H51">
+        <v>36.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>10.1</v>
+      </c>
+      <c r="K51">
+        <v>3.14</v>
+      </c>
+      <c r="L51">
+        <v>6.96</v>
+      </c>
+      <c r="M51">
+        <v>8.169123200000001</v>
+      </c>
+      <c r="N51">
+        <v>-1.209123200000001</v>
+      </c>
+      <c r="O51">
+        <v>-0.3566913440000003</v>
+      </c>
+      <c r="P51">
+        <v>-0.852431856000001</v>
+      </c>
+      <c r="Q51">
+        <v>2.287568143999999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1959707444525516</v>
+      </c>
+      <c r="T51">
+        <v>1.812161018665529</v>
+      </c>
+      <c r="U51">
+        <v>0.1966</v>
+      </c>
+      <c r="V51">
+        <v>0.251336642835794</v>
+      </c>
+      <c r="W51">
+        <v>0.1471872160184829</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.851988619782353</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.173644815519858</v>
+      </c>
+      <c r="C52">
+        <v>14.70800214736746</v>
+      </c>
+      <c r="D52">
+        <v>45.50800214736746</v>
+      </c>
+      <c r="E52">
+        <v>-6.299999999999997</v>
+      </c>
+      <c r="F52">
+        <v>42.40000000000001</v>
+      </c>
+      <c r="G52">
+        <v>11.6</v>
+      </c>
+      <c r="H52">
+        <v>36.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>10.1</v>
+      </c>
+      <c r="K52">
+        <v>3.14</v>
+      </c>
+      <c r="L52">
+        <v>6.96</v>
+      </c>
+      <c r="M52">
+        <v>8.335840000000001</v>
+      </c>
+      <c r="N52">
+        <v>-1.375840000000001</v>
+      </c>
+      <c r="O52">
+        <v>-0.4058728000000002</v>
+      </c>
+      <c r="P52">
+        <v>-0.9699672000000008</v>
+      </c>
+      <c r="Q52">
+        <v>2.170032799999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1991141593416027</v>
+      </c>
+      <c r="T52">
+        <v>1.84840423903884</v>
+      </c>
+      <c r="U52">
+        <v>0.1966</v>
+      </c>
+      <c r="V52">
+        <v>0.2463099099790782</v>
+      </c>
+      <c r="W52">
+        <v>0.1481754716981132</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.8349488473867059</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1752228155198579</v>
+      </c>
+      <c r="C53">
+        <v>13.33361198957093</v>
+      </c>
+      <c r="D53">
+        <v>44.98161198957094</v>
+      </c>
+      <c r="E53">
+        <v>-5.451999999999998</v>
+      </c>
+      <c r="F53">
+        <v>43.248</v>
+      </c>
+      <c r="G53">
+        <v>11.6</v>
+      </c>
+      <c r="H53">
+        <v>36.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>10.1</v>
+      </c>
+      <c r="K53">
+        <v>3.14</v>
+      </c>
+      <c r="L53">
+        <v>6.96</v>
+      </c>
+      <c r="M53">
+        <v>8.502556800000001</v>
+      </c>
+      <c r="N53">
+        <v>-1.542556800000001</v>
+      </c>
+      <c r="O53">
+        <v>-0.4550542560000001</v>
+      </c>
+      <c r="P53">
+        <v>-1.087502544000001</v>
+      </c>
+      <c r="Q53">
+        <v>2.052497455999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2023858768791864</v>
+      </c>
+      <c r="T53">
+        <v>1.886126774529428</v>
+      </c>
+      <c r="U53">
+        <v>0.1966</v>
+      </c>
+      <c r="V53">
+        <v>0.2414803039010571</v>
+      </c>
+      <c r="W53">
+        <v>0.1491249722530522</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.8185773013595157</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1768008155198579</v>
+      </c>
+      <c r="C54">
+        <v>11.97126007467715</v>
+      </c>
+      <c r="D54">
+        <v>44.46726007467716</v>
+      </c>
+      <c r="E54">
+        <v>-4.603999999999992</v>
+      </c>
+      <c r="F54">
+        <v>44.09600000000001</v>
+      </c>
+      <c r="G54">
+        <v>11.6</v>
+      </c>
+      <c r="H54">
+        <v>36.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>10.1</v>
+      </c>
+      <c r="K54">
+        <v>3.14</v>
+      </c>
+      <c r="L54">
+        <v>6.96</v>
+      </c>
+      <c r="M54">
+        <v>8.669273600000002</v>
+      </c>
+      <c r="N54">
+        <v>-1.709273600000002</v>
+      </c>
+      <c r="O54">
+        <v>-0.5042357120000005</v>
+      </c>
+      <c r="P54">
+        <v>-1.205037888000002</v>
+      </c>
+      <c r="Q54">
+        <v>1.934962111999998</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2057939159808361</v>
+      </c>
+      <c r="T54">
+        <v>1.925421082332125</v>
+      </c>
+      <c r="U54">
+        <v>0.1966</v>
+      </c>
+      <c r="V54">
+        <v>0.2368364519029598</v>
+      </c>
+      <c r="W54">
+        <v>0.1500379535558781</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.8028354301795249</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1884005307486121</v>
+      </c>
+      <c r="C55">
+        <v>7.67536085073678</v>
+      </c>
+      <c r="D55">
+        <v>41.01936085073679</v>
+      </c>
+      <c r="E55">
+        <v>-3.755999999999993</v>
+      </c>
+      <c r="F55">
+        <v>44.94400000000001</v>
+      </c>
+      <c r="G55">
+        <v>11.6</v>
+      </c>
+      <c r="H55">
+        <v>36.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>10.1</v>
+      </c>
+      <c r="K55">
+        <v>3.14</v>
+      </c>
+      <c r="L55">
+        <v>6.96</v>
+      </c>
+      <c r="M55">
+        <v>9.609027200000002</v>
+      </c>
+      <c r="N55">
+        <v>-2.649027200000002</v>
+      </c>
+      <c r="O55">
+        <v>-0.7814630240000003</v>
+      </c>
+      <c r="P55">
+        <v>-1.867564176000001</v>
+      </c>
+      <c r="Q55">
+        <v>1.272435823999998</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2112740317011819</v>
+      </c>
+      <c r="T55">
+        <v>1.988606200661731</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.2136740751446722</v>
+      </c>
+      <c r="W55">
+        <v>0.1681164827340691</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.7243188987954992</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1901505307486121</v>
+      </c>
+      <c r="C56">
+        <v>6.353071919381662</v>
+      </c>
+      <c r="D56">
+        <v>40.54507191938167</v>
+      </c>
+      <c r="E56">
+        <v>-2.907999999999994</v>
+      </c>
+      <c r="F56">
+        <v>45.79200000000001</v>
+      </c>
+      <c r="G56">
+        <v>11.6</v>
+      </c>
+      <c r="H56">
+        <v>36.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>10.1</v>
+      </c>
+      <c r="K56">
+        <v>3.14</v>
+      </c>
+      <c r="L56">
+        <v>6.96</v>
+      </c>
+      <c r="M56">
+        <v>9.790329600000002</v>
+      </c>
+      <c r="N56">
+        <v>-2.830329600000002</v>
+      </c>
+      <c r="O56">
+        <v>-0.8349472320000002</v>
+      </c>
+      <c r="P56">
+        <v>-1.995382368000001</v>
+      </c>
+      <c r="Q56">
+        <v>1.144617631999998</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2150234671729468</v>
+      </c>
+      <c r="T56">
+        <v>2.031836770241334</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.2097171478271783</v>
+      </c>
+      <c r="W56">
+        <v>0.1689624737945493</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.7109055858548419</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1919005307486121</v>
+      </c>
+      <c r="C57">
+        <v>5.041625610528413</v>
+      </c>
+      <c r="D57">
+        <v>40.08162561052842</v>
+      </c>
+      <c r="E57">
+        <v>-2.059999999999995</v>
+      </c>
+      <c r="F57">
+        <v>46.64000000000001</v>
+      </c>
+      <c r="G57">
+        <v>11.6</v>
+      </c>
+      <c r="H57">
+        <v>36.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>10.1</v>
+      </c>
+      <c r="K57">
+        <v>3.14</v>
+      </c>
+      <c r="L57">
+        <v>6.96</v>
+      </c>
+      <c r="M57">
+        <v>9.971632000000001</v>
+      </c>
+      <c r="N57">
+        <v>-3.011632000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.8884314400000002</v>
+      </c>
+      <c r="P57">
+        <v>-2.123200560000001</v>
+      </c>
+      <c r="Q57">
+        <v>1.016799439999998</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2189395442212345</v>
+      </c>
+      <c r="T57">
+        <v>2.07698869846892</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.205904108775775</v>
+      </c>
+      <c r="W57">
+        <v>0.1697777015437393</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.6979800297483901</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1936505307486121</v>
+      </c>
+      <c r="C58">
+        <v>3.740654319572386</v>
+      </c>
+      <c r="D58">
+        <v>39.6286543195724</v>
+      </c>
+      <c r="E58">
+        <v>-1.211999999999989</v>
+      </c>
+      <c r="F58">
+        <v>47.48800000000001</v>
+      </c>
+      <c r="G58">
+        <v>11.6</v>
+      </c>
+      <c r="H58">
+        <v>36.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>10.1</v>
+      </c>
+      <c r="K58">
+        <v>3.14</v>
+      </c>
+      <c r="L58">
+        <v>6.96</v>
+      </c>
+      <c r="M58">
+        <v>10.1529344</v>
+      </c>
+      <c r="N58">
+        <v>-3.192934400000003</v>
+      </c>
+      <c r="O58">
+        <v>-0.9419156480000007</v>
+      </c>
+      <c r="P58">
+        <v>-2.251018752000002</v>
+      </c>
+      <c r="Q58">
+        <v>0.8889812479999972</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2230336247717171</v>
+      </c>
+      <c r="T58">
+        <v>2.124192987070486</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.2022272496904933</v>
+      </c>
+      <c r="W58">
+        <v>0.1705638140161725</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.6855161006457402</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1954005307486121</v>
+      </c>
+      <c r="C59">
+        <v>2.449806873732122</v>
+      </c>
+      <c r="D59">
+        <v>39.18580687373213</v>
+      </c>
+      <c r="E59">
+        <v>-0.3639999999999901</v>
+      </c>
+      <c r="F59">
+        <v>48.33600000000001</v>
+      </c>
+      <c r="G59">
+        <v>11.6</v>
+      </c>
+      <c r="H59">
+        <v>36.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>10.1</v>
+      </c>
+      <c r="K59">
+        <v>3.14</v>
+      </c>
+      <c r="L59">
+        <v>6.96</v>
+      </c>
+      <c r="M59">
+        <v>10.3342368</v>
+      </c>
+      <c r="N59">
+        <v>-3.374236800000003</v>
+      </c>
+      <c r="O59">
+        <v>-0.9953998560000006</v>
+      </c>
+      <c r="P59">
+        <v>-2.378836944000002</v>
+      </c>
+      <c r="Q59">
+        <v>0.7611630559999973</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2273181276733849</v>
+      </c>
+      <c r="T59">
+        <v>2.173592823979102</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1986794032046952</v>
+      </c>
+      <c r="W59">
+        <v>0.1713223435948361</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.6734895023887975</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1971505307486121</v>
+      </c>
+      <c r="C60">
+        <v>1.168747624073561</v>
+      </c>
+      <c r="D60">
+        <v>38.75274762407356</v>
+      </c>
+      <c r="E60">
+        <v>0.4840000000000018</v>
+      </c>
+      <c r="F60">
+        <v>49.184</v>
+      </c>
+      <c r="G60">
+        <v>11.6</v>
+      </c>
+      <c r="H60">
+        <v>36.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>10.1</v>
+      </c>
+      <c r="K60">
+        <v>3.14</v>
+      </c>
+      <c r="L60">
+        <v>6.96</v>
+      </c>
+      <c r="M60">
+        <v>10.5155392</v>
+      </c>
+      <c r="N60">
+        <v>-3.555539200000001</v>
+      </c>
+      <c r="O60">
+        <v>-1.048884064</v>
+      </c>
+      <c r="P60">
+        <v>-2.506655136000001</v>
+      </c>
+      <c r="Q60">
+        <v>0.6333448639999988</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2318066545227512</v>
+      </c>
+      <c r="T60">
+        <v>2.225345034073842</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.1952538962528901</v>
+      </c>
+      <c r="W60">
+        <v>0.1720547169811321</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.6618776144165769</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1989005307486121</v>
+      </c>
+      <c r="C61">
+        <v>-0.102844402917377</v>
+      </c>
+      <c r="D61">
+        <v>38.32915559708263</v>
+      </c>
+      <c r="E61">
+        <v>1.332000000000001</v>
+      </c>
+      <c r="F61">
+        <v>50.032</v>
+      </c>
+      <c r="G61">
+        <v>11.6</v>
+      </c>
+      <c r="H61">
+        <v>36.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>10.1</v>
+      </c>
+      <c r="K61">
+        <v>3.14</v>
+      </c>
+      <c r="L61">
+        <v>6.96</v>
+      </c>
+      <c r="M61">
+        <v>10.6968416</v>
+      </c>
+      <c r="N61">
+        <v>-3.736841600000001</v>
+      </c>
+      <c r="O61">
+        <v>-1.102368272</v>
+      </c>
+      <c r="P61">
+        <v>-2.634473328000001</v>
+      </c>
+      <c r="Q61">
+        <v>0.5055266719999989</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2365141339013549</v>
+      </c>
+      <c r="T61">
+        <v>2.279621742221984</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1919445081808072</v>
+      </c>
+      <c r="W61">
+        <v>0.1727622641509434</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.6506593497654485</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2006505307486121</v>
+      </c>
+      <c r="C62">
+        <v>-1.365276298720538</v>
+      </c>
+      <c r="D62">
+        <v>37.91472370127946</v>
+      </c>
+      <c r="E62">
+        <v>2.18</v>
+      </c>
+      <c r="F62">
+        <v>50.88</v>
+      </c>
+      <c r="G62">
+        <v>11.6</v>
+      </c>
+      <c r="H62">
+        <v>36.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>10.1</v>
+      </c>
+      <c r="K62">
+        <v>3.14</v>
+      </c>
+      <c r="L62">
+        <v>6.96</v>
+      </c>
+      <c r="M62">
+        <v>10.878144</v>
+      </c>
+      <c r="N62">
+        <v>-3.918144000000001</v>
+      </c>
+      <c r="O62">
+        <v>-1.15585248</v>
+      </c>
+      <c r="P62">
+        <v>-2.762291520000001</v>
+      </c>
+      <c r="Q62">
+        <v>0.377708479999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2414569872488888</v>
+      </c>
+      <c r="T62">
+        <v>2.336612285777534</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1887454330444605</v>
+      </c>
+      <c r="W62">
+        <v>0.1734462264150944</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.6398150272693577</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2024005307486121</v>
+      </c>
+      <c r="C63">
+        <v>-2.618842015247417</v>
+      </c>
+      <c r="D63">
+        <v>37.50915798475259</v>
+      </c>
+      <c r="E63">
+        <v>3.028000000000006</v>
+      </c>
+      <c r="F63">
+        <v>51.72800000000001</v>
+      </c>
+      <c r="G63">
+        <v>11.6</v>
+      </c>
+      <c r="H63">
+        <v>36.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>10.1</v>
+      </c>
+      <c r="K63">
+        <v>3.14</v>
+      </c>
+      <c r="L63">
+        <v>6.96</v>
+      </c>
+      <c r="M63">
+        <v>11.0594464</v>
+      </c>
+      <c r="N63">
+        <v>-4.099446400000001</v>
+      </c>
+      <c r="O63">
+        <v>-1.209336688</v>
+      </c>
+      <c r="P63">
+        <v>-2.890109712000001</v>
+      </c>
+      <c r="Q63">
+        <v>0.2498902879999987</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2466533202552705</v>
+      </c>
+      <c r="T63">
+        <v>2.396525421310291</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.1856512456175021</v>
+      </c>
+      <c r="W63">
+        <v>0.174107763686978</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.6293262563305158</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2041505307486121</v>
+      </c>
+      <c r="C64">
+        <v>-3.863823060159291</v>
+      </c>
+      <c r="D64">
+        <v>37.11217693984072</v>
+      </c>
+      <c r="E64">
+        <v>3.876000000000005</v>
+      </c>
+      <c r="F64">
+        <v>52.57600000000001</v>
+      </c>
+      <c r="G64">
+        <v>11.6</v>
+      </c>
+      <c r="H64">
+        <v>36.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>10.1</v>
+      </c>
+      <c r="K64">
+        <v>3.14</v>
+      </c>
+      <c r="L64">
+        <v>6.96</v>
+      </c>
+      <c r="M64">
+        <v>11.2407488</v>
+      </c>
+      <c r="N64">
+        <v>-4.2807488</v>
+      </c>
+      <c r="O64">
+        <v>-1.262820896</v>
+      </c>
+      <c r="P64">
+        <v>-3.017927904</v>
+      </c>
+      <c r="Q64">
+        <v>0.1220720959999992</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2521231444725145</v>
+      </c>
+      <c r="T64">
+        <v>2.459591879765825</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.1826568706881876</v>
+      </c>
+      <c r="W64">
+        <v>0.1747479610468655</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.6191758328413139</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2059005307486121</v>
+      </c>
+      <c r="C65">
+        <v>-5.10048914849402</v>
+      </c>
+      <c r="D65">
+        <v>36.72351085150598</v>
+      </c>
+      <c r="E65">
+        <v>4.724000000000004</v>
+      </c>
+      <c r="F65">
+        <v>53.42400000000001</v>
+      </c>
+      <c r="G65">
+        <v>11.6</v>
+      </c>
+      <c r="H65">
+        <v>36.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>10.1</v>
+      </c>
+      <c r="K65">
+        <v>3.14</v>
+      </c>
+      <c r="L65">
+        <v>6.96</v>
+      </c>
+      <c r="M65">
+        <v>11.4220512</v>
+      </c>
+      <c r="N65">
+        <v>-4.4620512</v>
+      </c>
+      <c r="O65">
+        <v>-1.316305104</v>
+      </c>
+      <c r="P65">
+        <v>-3.145746096000001</v>
+      </c>
+      <c r="Q65">
+        <v>-0.005746096000001089</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2578886348636635</v>
+      </c>
+      <c r="T65">
+        <v>2.526067335975712</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.1797575552804385</v>
+      </c>
+      <c r="W65">
+        <v>0.1753678346810422</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.6093476450184359</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2076505307486121</v>
+      </c>
+      <c r="C66">
+        <v>-6.329098813771388</v>
+      </c>
+      <c r="D66">
+        <v>36.34290118622862</v>
+      </c>
+      <c r="E66">
+        <v>5.572000000000003</v>
+      </c>
+      <c r="F66">
+        <v>54.27200000000001</v>
+      </c>
+      <c r="G66">
+        <v>11.6</v>
+      </c>
+      <c r="H66">
+        <v>36.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>10.1</v>
+      </c>
+      <c r="K66">
+        <v>3.14</v>
+      </c>
+      <c r="L66">
+        <v>6.96</v>
+      </c>
+      <c r="M66">
+        <v>11.6033536</v>
+      </c>
+      <c r="N66">
+        <v>-4.6433536</v>
+      </c>
+      <c r="O66">
+        <v>-1.369789312</v>
+      </c>
+      <c r="P66">
+        <v>-3.273564288</v>
+      </c>
+      <c r="Q66">
+        <v>-0.1335642880000005</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2639744302765431</v>
+      </c>
+      <c r="T66">
+        <v>2.596235873086149</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.1769488434791817</v>
+      </c>
+      <c r="W66">
+        <v>0.175968337264151</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5998265880650229</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2094005307486121</v>
+      </c>
+      <c r="C67">
+        <v>-7.549899981486504</v>
+      </c>
+      <c r="D67">
+        <v>35.97010001851351</v>
+      </c>
+      <c r="E67">
+        <v>6.420000000000009</v>
+      </c>
+      <c r="F67">
+        <v>55.12000000000001</v>
+      </c>
+      <c r="G67">
+        <v>11.6</v>
+      </c>
+      <c r="H67">
+        <v>36.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>10.1</v>
+      </c>
+      <c r="K67">
+        <v>3.14</v>
+      </c>
+      <c r="L67">
+        <v>6.96</v>
+      </c>
+      <c r="M67">
+        <v>11.784656</v>
+      </c>
+      <c r="N67">
+        <v>-4.824656000000002</v>
+      </c>
+      <c r="O67">
+        <v>-1.42327352</v>
+      </c>
+      <c r="P67">
+        <v>-3.401382480000001</v>
+      </c>
+      <c r="Q67">
+        <v>-0.2613824800000017</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2704079854273015</v>
+      </c>
+      <c r="T67">
+        <v>2.67041404088861</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.174226553579502</v>
+      </c>
+      <c r="W67">
+        <v>0.1765503628447025</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5905984867101763</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2111505307486121</v>
+      </c>
+      <c r="C68">
+        <v>-8.763130507664656</v>
+      </c>
+      <c r="D68">
+        <v>35.60486949233535</v>
+      </c>
+      <c r="E68">
+        <v>7.268000000000008</v>
+      </c>
+      <c r="F68">
+        <v>55.96800000000001</v>
+      </c>
+      <c r="G68">
+        <v>11.6</v>
+      </c>
+      <c r="H68">
+        <v>36.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>10.1</v>
+      </c>
+      <c r="K68">
+        <v>3.14</v>
+      </c>
+      <c r="L68">
+        <v>6.96</v>
+      </c>
+      <c r="M68">
+        <v>11.9659584</v>
+      </c>
+      <c r="N68">
+        <v>-5.005958400000002</v>
+      </c>
+      <c r="O68">
+        <v>-1.476757728</v>
+      </c>
+      <c r="P68">
+        <v>-3.529200672000002</v>
+      </c>
+      <c r="Q68">
+        <v>-0.3892006720000021</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2772199849986927</v>
+      </c>
+      <c r="T68">
+        <v>2.748955630326511</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.1715867573131459</v>
+      </c>
+      <c r="W68">
+        <v>0.1771147512864494</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5816500247903251</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2129005307486121</v>
+      </c>
+      <c r="C69">
+        <v>-9.969018684935953</v>
+      </c>
+      <c r="D69">
+        <v>35.24698131506405</v>
+      </c>
+      <c r="E69">
+        <v>8.116000000000007</v>
+      </c>
+      <c r="F69">
+        <v>56.81600000000001</v>
+      </c>
+      <c r="G69">
+        <v>11.6</v>
+      </c>
+      <c r="H69">
+        <v>36.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>10.1</v>
+      </c>
+      <c r="K69">
+        <v>3.14</v>
+      </c>
+      <c r="L69">
+        <v>6.96</v>
+      </c>
+      <c r="M69">
+        <v>12.1472608</v>
+      </c>
+      <c r="N69">
+        <v>-5.187260800000002</v>
+      </c>
+      <c r="O69">
+        <v>-1.530241936</v>
+      </c>
+      <c r="P69">
+        <v>-3.657018864000001</v>
+      </c>
+      <c r="Q69">
+        <v>-0.5170188640000015</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2844448330289561</v>
+      </c>
+      <c r="T69">
+        <v>2.832257316093981</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.1690257609353377</v>
+      </c>
+      <c r="W69">
+        <v>0.1776622923120248</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5729686811367382</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2146505307486121</v>
+      </c>
+      <c r="C70">
+        <v>-11.16778371839235</v>
+      </c>
+      <c r="D70">
+        <v>34.89621628160766</v>
+      </c>
+      <c r="E70">
+        <v>8.964000000000006</v>
+      </c>
+      <c r="F70">
+        <v>57.66400000000001</v>
+      </c>
+      <c r="G70">
+        <v>11.6</v>
+      </c>
+      <c r="H70">
+        <v>36.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>10.1</v>
+      </c>
+      <c r="K70">
+        <v>3.14</v>
+      </c>
+      <c r="L70">
+        <v>6.96</v>
+      </c>
+      <c r="M70">
+        <v>12.3285632</v>
+      </c>
+      <c r="N70">
+        <v>-5.368563200000001</v>
+      </c>
+      <c r="O70">
+        <v>-1.583726144</v>
+      </c>
+      <c r="P70">
+        <v>-3.784837056000002</v>
+      </c>
+      <c r="Q70">
+        <v>-0.6448370560000019</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.292121234061111</v>
+      </c>
+      <c r="T70">
+        <v>2.920765357221918</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.1665400879804063</v>
+      </c>
+      <c r="W70">
+        <v>0.1781937291897891</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5645426711200214</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2164005307486121</v>
+      </c>
+      <c r="C71">
+        <v>-12.35963617331128</v>
+      </c>
+      <c r="D71">
+        <v>34.55236382668873</v>
+      </c>
+      <c r="E71">
+        <v>9.812000000000012</v>
+      </c>
+      <c r="F71">
+        <v>58.51200000000001</v>
+      </c>
+      <c r="G71">
+        <v>11.6</v>
+      </c>
+      <c r="H71">
+        <v>36.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>10.1</v>
+      </c>
+      <c r="K71">
+        <v>3.14</v>
+      </c>
+      <c r="L71">
+        <v>6.96</v>
+      </c>
+      <c r="M71">
+        <v>12.5098656</v>
+      </c>
+      <c r="N71">
+        <v>-5.549865600000003</v>
+      </c>
+      <c r="O71">
+        <v>-1.637210352000001</v>
+      </c>
+      <c r="P71">
+        <v>-3.912655248000003</v>
+      </c>
+      <c r="Q71">
+        <v>-0.7726552480000031</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3002928867727598</v>
+      </c>
+      <c r="T71">
+        <v>3.014983594551658</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.1641264635169221</v>
+      </c>
+      <c r="W71">
+        <v>0.178709762100082</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5563608932777022</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2181505307486121</v>
+      </c>
+      <c r="C72">
+        <v>-13.5447783966675</v>
+      </c>
+      <c r="D72">
+        <v>34.21522160333252</v>
+      </c>
+      <c r="E72">
+        <v>10.66000000000001</v>
+      </c>
+      <c r="F72">
+        <v>59.36000000000001</v>
+      </c>
+      <c r="G72">
+        <v>11.6</v>
+      </c>
+      <c r="H72">
+        <v>36.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>10.1</v>
+      </c>
+      <c r="K72">
+        <v>3.14</v>
+      </c>
+      <c r="L72">
+        <v>6.96</v>
+      </c>
+      <c r="M72">
+        <v>12.691168</v>
+      </c>
+      <c r="N72">
+        <v>-5.731168000000003</v>
+      </c>
+      <c r="O72">
+        <v>-1.690694560000001</v>
+      </c>
+      <c r="P72">
+        <v>-4.040473440000002</v>
+      </c>
+      <c r="Q72">
+        <v>-0.9004734400000025</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3090093163318517</v>
+      </c>
+      <c r="T72">
+        <v>3.115483047703379</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.1617817997523947</v>
+      </c>
+      <c r="W72">
+        <v>0.179211051212938</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5484128805165922</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2199005307486121</v>
+      </c>
+      <c r="C73">
+        <v>-14.72340491420623</v>
+      </c>
+      <c r="D73">
+        <v>33.88459508579377</v>
+      </c>
+      <c r="E73">
+        <v>11.508</v>
+      </c>
+      <c r="F73">
+        <v>60.20800000000001</v>
+      </c>
+      <c r="G73">
+        <v>11.6</v>
+      </c>
+      <c r="H73">
+        <v>36.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>10.1</v>
+      </c>
+      <c r="K73">
+        <v>3.14</v>
+      </c>
+      <c r="L73">
+        <v>6.96</v>
+      </c>
+      <c r="M73">
+        <v>12.8724704</v>
+      </c>
+      <c r="N73">
+        <v>-5.912470400000001</v>
+      </c>
+      <c r="O73">
+        <v>-1.744178768</v>
+      </c>
+      <c r="P73">
+        <v>-4.168291632000001</v>
+      </c>
+      <c r="Q73">
+        <v>-1.028291632000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3183268789639845</v>
+      </c>
+      <c r="T73">
+        <v>3.222913497624185</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.1595031828544737</v>
+      </c>
+      <c r="W73">
+        <v>0.1796982195057135</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5406887554388937</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2216505307486121</v>
+      </c>
+      <c r="C74">
+        <v>-15.89570280471476</v>
+      </c>
+      <c r="D74">
+        <v>33.56029719528524</v>
+      </c>
+      <c r="E74">
+        <v>12.356</v>
+      </c>
+      <c r="F74">
+        <v>61.056</v>
+      </c>
+      <c r="G74">
+        <v>11.6</v>
+      </c>
+      <c r="H74">
+        <v>36.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>10.1</v>
+      </c>
+      <c r="K74">
+        <v>3.14</v>
+      </c>
+      <c r="L74">
+        <v>6.96</v>
+      </c>
+      <c r="M74">
+        <v>13.0537728</v>
+      </c>
+      <c r="N74">
+        <v>-6.093772800000001</v>
+      </c>
+      <c r="O74">
+        <v>-1.797662976</v>
+      </c>
+      <c r="P74">
+        <v>-4.296109824000001</v>
+      </c>
+      <c r="Q74">
+        <v>-1.156109824000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3283099817841268</v>
+      </c>
+      <c r="T74">
+        <v>3.338017551110763</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.1572878608703837</v>
+      </c>
+      <c r="W74">
+        <v>0.180171855345912</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5331791893911314</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2234005307486121</v>
+      </c>
+      <c r="C75">
+        <v>-17.06185205300553</v>
+      </c>
+      <c r="D75">
+        <v>33.24214794699447</v>
+      </c>
+      <c r="E75">
+        <v>13.204</v>
+      </c>
+      <c r="F75">
+        <v>61.904</v>
+      </c>
+      <c r="G75">
+        <v>11.6</v>
+      </c>
+      <c r="H75">
+        <v>36.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>10.1</v>
+      </c>
+      <c r="K75">
+        <v>3.14</v>
+      </c>
+      <c r="L75">
+        <v>6.96</v>
+      </c>
+      <c r="M75">
+        <v>13.2350752</v>
+      </c>
+      <c r="N75">
+        <v>-6.275075200000001</v>
+      </c>
+      <c r="O75">
+        <v>-1.851147184</v>
+      </c>
+      <c r="P75">
+        <v>-4.423928016000001</v>
+      </c>
+      <c r="Q75">
+        <v>-1.283928016000002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3390325737020574</v>
+      </c>
+      <c r="T75">
+        <v>3.461647830781532</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.1551332326392826</v>
+      </c>
+      <c r="W75">
+        <v>0.1806325148617214</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5258753648789241</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2251505307486121</v>
+      </c>
+      <c r="C76">
+        <v>-18.22202588301045</v>
+      </c>
+      <c r="D76">
+        <v>32.92997411698956</v>
+      </c>
+      <c r="E76">
+        <v>14.05200000000001</v>
+      </c>
+      <c r="F76">
+        <v>62.75200000000001</v>
+      </c>
+      <c r="G76">
+        <v>11.6</v>
+      </c>
+      <c r="H76">
+        <v>36.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>10.1</v>
+      </c>
+      <c r="K76">
+        <v>3.14</v>
+      </c>
+      <c r="L76">
+        <v>6.96</v>
+      </c>
+      <c r="M76">
+        <v>13.4163776</v>
+      </c>
+      <c r="N76">
+        <v>-6.456377600000001</v>
+      </c>
+      <c r="O76">
+        <v>-1.904631392</v>
+      </c>
+      <c r="P76">
+        <v>-4.551746208000001</v>
+      </c>
+      <c r="Q76">
+        <v>-1.411746208000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3505799803829058</v>
+      </c>
+      <c r="T76">
+        <v>3.594788131965436</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.1530368376036166</v>
+      </c>
+      <c r="W76">
+        <v>0.1810807241203468</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5187689410292089</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2269005307486121</v>
+      </c>
+      <c r="C77">
+        <v>-19.37639107228121</v>
+      </c>
+      <c r="D77">
+        <v>32.6236089277188</v>
+      </c>
+      <c r="E77">
+        <v>14.90000000000001</v>
+      </c>
+      <c r="F77">
+        <v>63.60000000000001</v>
+      </c>
+      <c r="G77">
+        <v>11.6</v>
+      </c>
+      <c r="H77">
+        <v>36.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>10.1</v>
+      </c>
+      <c r="K77">
+        <v>3.14</v>
+      </c>
+      <c r="L77">
+        <v>6.96</v>
+      </c>
+      <c r="M77">
+        <v>13.59768</v>
+      </c>
+      <c r="N77">
+        <v>-6.63768</v>
+      </c>
+      <c r="O77">
+        <v>-1.9581156</v>
+      </c>
+      <c r="P77">
+        <v>-4.6795644</v>
+      </c>
+      <c r="Q77">
+        <v>-1.539564400000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.363051179598222</v>
+      </c>
+      <c r="T77">
+        <v>3.738579657244054</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.1509963464355684</v>
+      </c>
+      <c r="W77">
+        <v>0.1815169811320755</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5118520218154862</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2286505307486121</v>
+      </c>
+      <c r="C78">
+        <v>-20.52510824909599</v>
+      </c>
+      <c r="D78">
+        <v>32.32289175090402</v>
+      </c>
+      <c r="E78">
+        <v>15.748</v>
+      </c>
+      <c r="F78">
+        <v>64.44800000000001</v>
+      </c>
+      <c r="G78">
+        <v>11.6</v>
+      </c>
+      <c r="H78">
+        <v>36.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>10.1</v>
+      </c>
+      <c r="K78">
+        <v>3.14</v>
+      </c>
+      <c r="L78">
+        <v>6.96</v>
+      </c>
+      <c r="M78">
+        <v>13.7789824</v>
+      </c>
+      <c r="N78">
+        <v>-6.8189824</v>
+      </c>
+      <c r="O78">
+        <v>-2.011599808</v>
+      </c>
+      <c r="P78">
+        <v>-4.807382592000001</v>
+      </c>
+      <c r="Q78">
+        <v>-1.667382592000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3765616454148146</v>
+      </c>
+      <c r="T78">
+        <v>3.894353809629223</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.1490095524035214</v>
+      </c>
+      <c r="W78">
+        <v>0.1819417576961271</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5051171267915981</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2507343389245029</v>
+      </c>
+      <c r="C79">
+        <v>-24.74119170711138</v>
+      </c>
+      <c r="D79">
+        <v>28.95480829288862</v>
+      </c>
+      <c r="E79">
+        <v>16.596</v>
+      </c>
+      <c r="F79">
+        <v>65.29600000000001</v>
+      </c>
+      <c r="G79">
+        <v>11.6</v>
+      </c>
+      <c r="H79">
+        <v>36.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>10.1</v>
+      </c>
+      <c r="K79">
+        <v>3.14</v>
+      </c>
+      <c r="L79">
+        <v>6.96</v>
+      </c>
+      <c r="M79">
+        <v>15.5926848</v>
+      </c>
+      <c r="N79">
+        <v>-8.632684800000003</v>
+      </c>
+      <c r="O79">
+        <v>-2.546642016</v>
+      </c>
+      <c r="P79">
+        <v>-6.086042784000004</v>
+      </c>
+      <c r="Q79">
+        <v>-2.946042784000004</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3959591438062882</v>
+      </c>
+      <c r="T79">
+        <v>4.118004785942233</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.131677131060842</v>
+      </c>
+      <c r="W79">
+        <v>0.207355501102671</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4463631561384476</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2527343389245029</v>
+      </c>
+      <c r="C80">
+        <v>-25.85988044682892</v>
+      </c>
+      <c r="D80">
+        <v>28.68411955317109</v>
+      </c>
+      <c r="E80">
+        <v>17.444</v>
+      </c>
+      <c r="F80">
+        <v>66.14400000000001</v>
+      </c>
+      <c r="G80">
+        <v>11.6</v>
+      </c>
+      <c r="H80">
+        <v>36.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>10.1</v>
+      </c>
+      <c r="K80">
+        <v>3.14</v>
+      </c>
+      <c r="L80">
+        <v>6.96</v>
+      </c>
+      <c r="M80">
+        <v>15.7951872</v>
+      </c>
+      <c r="N80">
+        <v>-8.835187200000004</v>
+      </c>
+      <c r="O80">
+        <v>-2.606380224</v>
+      </c>
+      <c r="P80">
+        <v>-6.228806976000003</v>
+      </c>
+      <c r="Q80">
+        <v>-3.088806976000003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4121936503429377</v>
+      </c>
+      <c r="T80">
+        <v>4.30518682166688</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.1299889627139081</v>
+      </c>
+      <c r="W80">
+        <v>0.2077586357039188</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.44064055157257</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2547343389245029</v>
+      </c>
+      <c r="C81">
+        <v>-26.97355490783441</v>
+      </c>
+      <c r="D81">
+        <v>28.41844509216561</v>
+      </c>
+      <c r="E81">
+        <v>18.29200000000002</v>
+      </c>
+      <c r="F81">
+        <v>66.99200000000002</v>
+      </c>
+      <c r="G81">
+        <v>11.6</v>
+      </c>
+      <c r="H81">
+        <v>36.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>10.1</v>
+      </c>
+      <c r="K81">
+        <v>3.14</v>
+      </c>
+      <c r="L81">
+        <v>6.96</v>
+      </c>
+      <c r="M81">
+        <v>15.9976896</v>
+      </c>
+      <c r="N81">
+        <v>-9.037689600000004</v>
+      </c>
+      <c r="O81">
+        <v>-2.666118432000001</v>
+      </c>
+      <c r="P81">
+        <v>-6.371571168000003</v>
+      </c>
+      <c r="Q81">
+        <v>-3.231571168000003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4299743003592681</v>
+      </c>
+      <c r="T81">
+        <v>4.510195717936733</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.1283435328061371</v>
+      </c>
+      <c r="W81">
+        <v>0.2081515643658945</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.4350628230716514</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2567343389245029</v>
+      </c>
+      <c r="C82">
+        <v>-28.08235313937892</v>
+      </c>
+      <c r="D82">
+        <v>28.1576468606211</v>
+      </c>
+      <c r="E82">
+        <v>19.14000000000001</v>
+      </c>
+      <c r="F82">
+        <v>67.84000000000002</v>
+      </c>
+      <c r="G82">
+        <v>11.6</v>
+      </c>
+      <c r="H82">
+        <v>36.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>10.1</v>
+      </c>
+      <c r="K82">
+        <v>3.14</v>
+      </c>
+      <c r="L82">
+        <v>6.96</v>
+      </c>
+      <c r="M82">
+        <v>16.200192</v>
+      </c>
+      <c r="N82">
+        <v>-9.240192000000004</v>
+      </c>
+      <c r="O82">
+        <v>-2.72585664</v>
+      </c>
+      <c r="P82">
+        <v>-6.514335360000004</v>
+      </c>
+      <c r="Q82">
+        <v>-3.374335360000004</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4495330153772316</v>
+      </c>
+      <c r="T82">
+        <v>4.735705503833569</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.1267392386460604</v>
+      </c>
+      <c r="W82">
+        <v>0.2085346698113208</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.4296245377832558</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2587343389245029</v>
+      </c>
+      <c r="C83">
+        <v>-29.18640816924205</v>
+      </c>
+      <c r="D83">
+        <v>27.90159183075797</v>
+      </c>
+      <c r="E83">
+        <v>19.98800000000001</v>
+      </c>
+      <c r="F83">
+        <v>68.68800000000002</v>
+      </c>
+      <c r="G83">
+        <v>11.6</v>
+      </c>
+      <c r="H83">
+        <v>36.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>10.1</v>
+      </c>
+      <c r="K83">
+        <v>3.14</v>
+      </c>
+      <c r="L83">
+        <v>6.96</v>
+      </c>
+      <c r="M83">
+        <v>16.40269440000001</v>
+      </c>
+      <c r="N83">
+        <v>-9.442694400000004</v>
+      </c>
+      <c r="O83">
+        <v>-2.785594848000001</v>
+      </c>
+      <c r="P83">
+        <v>-6.657099552000004</v>
+      </c>
+      <c r="Q83">
+        <v>-3.517099552000004</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.471150542502349</v>
+      </c>
+      <c r="T83">
+        <v>4.984953161930073</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.1251745566874671</v>
+      </c>
+      <c r="W83">
+        <v>0.2089083158630329</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4243205311439564</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2607343389245029</v>
+      </c>
+      <c r="C84">
+        <v>-30.28584822999127</v>
+      </c>
+      <c r="D84">
+        <v>27.65015177000875</v>
+      </c>
+      <c r="E84">
+        <v>20.83600000000001</v>
+      </c>
+      <c r="F84">
+        <v>69.53600000000002</v>
+      </c>
+      <c r="G84">
+        <v>11.6</v>
+      </c>
+      <c r="H84">
+        <v>36.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>10.1</v>
+      </c>
+      <c r="K84">
+        <v>3.14</v>
+      </c>
+      <c r="L84">
+        <v>6.96</v>
+      </c>
+      <c r="M84">
+        <v>16.60519680000001</v>
+      </c>
+      <c r="N84">
+        <v>-9.645196800000004</v>
+      </c>
+      <c r="O84">
+        <v>-2.845333056000001</v>
+      </c>
+      <c r="P84">
+        <v>-6.799863744000003</v>
+      </c>
+      <c r="Q84">
+        <v>-3.659863744000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4951700170858129</v>
+      </c>
+      <c r="T84">
+        <v>5.261895004259522</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.1236480377034736</v>
+      </c>
+      <c r="W84">
+        <v>0.2092728485964105</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.4191458905202495</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2627343389245029</v>
+      </c>
+      <c r="C85">
+        <v>-31.38079697311665</v>
+      </c>
+      <c r="D85">
+        <v>27.40320302688337</v>
+      </c>
+      <c r="E85">
+        <v>21.68400000000001</v>
+      </c>
+      <c r="F85">
+        <v>70.38400000000001</v>
+      </c>
+      <c r="G85">
+        <v>11.6</v>
+      </c>
+      <c r="H85">
+        <v>36.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>10.1</v>
+      </c>
+      <c r="K85">
+        <v>3.14</v>
+      </c>
+      <c r="L85">
+        <v>6.96</v>
+      </c>
+      <c r="M85">
+        <v>16.80769920000001</v>
+      </c>
+      <c r="N85">
+        <v>-9.847699200000005</v>
+      </c>
+      <c r="O85">
+        <v>-2.905071264</v>
+      </c>
+      <c r="P85">
+        <v>-6.942627936000004</v>
+      </c>
+      <c r="Q85">
+        <v>-3.802627936000005</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5220153122085077</v>
+      </c>
+      <c r="T85">
+        <v>5.571418239804199</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.1221583023094558</v>
+      </c>
+      <c r="W85">
+        <v>0.209628597408502</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.4140959400320537</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2647343389245029</v>
+      </c>
+      <c r="C86">
+        <v>-32.47137367179227</v>
+      </c>
+      <c r="D86">
+        <v>27.16062632820774</v>
+      </c>
+      <c r="E86">
+        <v>22.53200000000001</v>
+      </c>
+      <c r="F86">
+        <v>71.23200000000001</v>
+      </c>
+      <c r="G86">
+        <v>11.6</v>
+      </c>
+      <c r="H86">
+        <v>36.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>10.1</v>
+      </c>
+      <c r="K86">
+        <v>3.14</v>
+      </c>
+      <c r="L86">
+        <v>6.96</v>
+      </c>
+      <c r="M86">
+        <v>17.01020160000001</v>
+      </c>
+      <c r="N86">
+        <v>-10.0502016</v>
+      </c>
+      <c r="O86">
+        <v>-2.964809472000001</v>
+      </c>
+      <c r="P86">
+        <v>-7.085392128000004</v>
+      </c>
+      <c r="Q86">
+        <v>-3.945392128000004</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5522162692215393</v>
+      </c>
+      <c r="T86">
+        <v>5.919631879791959</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.1207040368057718</v>
+      </c>
+      <c r="W86">
+        <v>0.2099758760107817</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.4091662264602436</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2667343389245029</v>
+      </c>
+      <c r="C87">
+        <v>-33.55769341296303</v>
+      </c>
+      <c r="D87">
+        <v>26.92230658703699</v>
+      </c>
+      <c r="E87">
+        <v>23.38000000000001</v>
+      </c>
+      <c r="F87">
+        <v>72.08000000000001</v>
+      </c>
+      <c r="G87">
+        <v>11.6</v>
+      </c>
+      <c r="H87">
+        <v>36.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>10.1</v>
+      </c>
+      <c r="K87">
+        <v>3.14</v>
+      </c>
+      <c r="L87">
+        <v>6.96</v>
+      </c>
+      <c r="M87">
+        <v>17.212704</v>
+      </c>
+      <c r="N87">
+        <v>-10.252704</v>
+      </c>
+      <c r="O87">
+        <v>-3.02454768</v>
+      </c>
+      <c r="P87">
+        <v>-7.228156320000002</v>
+      </c>
+      <c r="Q87">
+        <v>-4.088156320000002</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5864440205029753</v>
+      </c>
+      <c r="T87">
+        <v>6.314274005111423</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.1192839893139392</v>
+      </c>
+      <c r="W87">
+        <v>0.2103149833518313</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.4043525061489467</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2687343389245029</v>
+      </c>
+      <c r="C88">
+        <v>-34.6398672794065</v>
+      </c>
+      <c r="D88">
+        <v>26.68813272059352</v>
+      </c>
+      <c r="E88">
+        <v>24.22800000000001</v>
+      </c>
+      <c r="F88">
+        <v>72.92800000000001</v>
+      </c>
+      <c r="G88">
+        <v>11.6</v>
+      </c>
+      <c r="H88">
+        <v>36.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>10.1</v>
+      </c>
+      <c r="K88">
+        <v>3.14</v>
+      </c>
+      <c r="L88">
+        <v>6.96</v>
+      </c>
+      <c r="M88">
+        <v>17.4152064</v>
+      </c>
+      <c r="N88">
+        <v>-10.4552064</v>
+      </c>
+      <c r="O88">
+        <v>-3.084285888</v>
+      </c>
+      <c r="P88">
+        <v>-7.370920512000001</v>
+      </c>
+      <c r="Q88">
+        <v>-4.230920512000002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.625561450538902</v>
+      </c>
+      <c r="T88">
+        <v>6.765293576905097</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.1178969661823818</v>
+      </c>
+      <c r="W88">
+        <v>0.2106462044756472</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3996507328216334</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2707343389245029</v>
+      </c>
+      <c r="C89">
+        <v>-35.71800252237524</v>
+      </c>
+      <c r="D89">
+        <v>26.45799747762477</v>
+      </c>
+      <c r="E89">
+        <v>25.07600000000001</v>
+      </c>
+      <c r="F89">
+        <v>73.77600000000001</v>
+      </c>
+      <c r="G89">
+        <v>11.6</v>
+      </c>
+      <c r="H89">
+        <v>36.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>10.1</v>
+      </c>
+      <c r="K89">
+        <v>3.14</v>
+      </c>
+      <c r="L89">
+        <v>6.96</v>
+      </c>
+      <c r="M89">
+        <v>17.6177088</v>
+      </c>
+      <c r="N89">
+        <v>-10.6577088</v>
+      </c>
+      <c r="O89">
+        <v>-3.144024096</v>
+      </c>
+      <c r="P89">
+        <v>-7.513684704000002</v>
+      </c>
+      <c r="Q89">
+        <v>-4.373684704000002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6706969467342021</v>
+      </c>
+      <c r="T89">
+        <v>7.285700775128565</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.1165418286400556</v>
+      </c>
+      <c r="W89">
+        <v>0.2109698113207547</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3950570462374767</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2727343389245029</v>
+      </c>
+      <c r="C90">
+        <v>-36.79220272538318</v>
+      </c>
+      <c r="D90">
+        <v>26.23179727461683</v>
+      </c>
+      <c r="E90">
+        <v>25.92400000000001</v>
+      </c>
+      <c r="F90">
+        <v>74.62400000000001</v>
+      </c>
+      <c r="G90">
+        <v>11.6</v>
+      </c>
+      <c r="H90">
+        <v>36.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>10.1</v>
+      </c>
+      <c r="K90">
+        <v>3.14</v>
+      </c>
+      <c r="L90">
+        <v>6.96</v>
+      </c>
+      <c r="M90">
+        <v>17.8202112</v>
+      </c>
+      <c r="N90">
+        <v>-10.8602112</v>
+      </c>
+      <c r="O90">
+        <v>-3.203762304</v>
+      </c>
+      <c r="P90">
+        <v>-7.656448896000002</v>
+      </c>
+      <c r="Q90">
+        <v>-4.516448896000003</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7233550256287191</v>
+      </c>
+      <c r="T90">
+        <v>7.892842506389281</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.1152174896782368</v>
+      </c>
+      <c r="W90">
+        <v>0.2112860634648371</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3905677616211417</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2747343389245029</v>
+      </c>
+      <c r="C91">
+        <v>-37.86256795966144</v>
+      </c>
+      <c r="D91">
+        <v>26.00943204033857</v>
+      </c>
+      <c r="E91">
+        <v>26.77200000000001</v>
+      </c>
+      <c r="F91">
+        <v>75.47200000000001</v>
+      </c>
+      <c r="G91">
+        <v>11.6</v>
+      </c>
+      <c r="H91">
+        <v>36.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>10.1</v>
+      </c>
+      <c r="K91">
+        <v>3.14</v>
+      </c>
+      <c r="L91">
+        <v>6.96</v>
+      </c>
+      <c r="M91">
+        <v>18.0227136</v>
+      </c>
+      <c r="N91">
+        <v>-11.0627136</v>
+      </c>
+      <c r="O91">
+        <v>-3.263500512</v>
+      </c>
+      <c r="P91">
+        <v>-7.799213088000002</v>
+      </c>
+      <c r="Q91">
+        <v>-4.659213088000002</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7855873006858753</v>
+      </c>
+      <c r="T91">
+        <v>8.610373643333761</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.1139229111425262</v>
+      </c>
+      <c r="W91">
+        <v>0.2115952088191648</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3861793598051738</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2767343389245029</v>
+      </c>
+      <c r="C92">
+        <v>-38.92919493177403</v>
+      </c>
+      <c r="D92">
+        <v>25.79080506822597</v>
+      </c>
+      <c r="E92">
+        <v>27.62</v>
+      </c>
+      <c r="F92">
+        <v>76.32000000000001</v>
+      </c>
+      <c r="G92">
+        <v>11.6</v>
+      </c>
+      <c r="H92">
+        <v>36.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>10.1</v>
+      </c>
+      <c r="K92">
+        <v>3.14</v>
+      </c>
+      <c r="L92">
+        <v>6.96</v>
+      </c>
+      <c r="M92">
+        <v>18.225216</v>
+      </c>
+      <c r="N92">
+        <v>-11.265216</v>
+      </c>
+      <c r="O92">
+        <v>-3.32323872</v>
+      </c>
+      <c r="P92">
+        <v>-7.941977280000002</v>
+      </c>
+      <c r="Q92">
+        <v>-4.801977280000003</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.860266030754463</v>
+      </c>
+      <c r="T92">
+        <v>9.471411007667136</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.1126571010187204</v>
+      </c>
+      <c r="W92">
+        <v>0.2118974842767296</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3818884780295608</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2787343389245029</v>
+      </c>
+      <c r="C93">
+        <v>-39.99217712385069</v>
+      </c>
+      <c r="D93">
+        <v>25.57582287614931</v>
+      </c>
+      <c r="E93">
+        <v>28.468</v>
+      </c>
+      <c r="F93">
+        <v>77.16800000000001</v>
+      </c>
+      <c r="G93">
+        <v>11.6</v>
+      </c>
+      <c r="H93">
+        <v>36.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>10.1</v>
+      </c>
+      <c r="K93">
+        <v>3.14</v>
+      </c>
+      <c r="L93">
+        <v>6.96</v>
+      </c>
+      <c r="M93">
+        <v>18.4277184</v>
+      </c>
+      <c r="N93">
+        <v>-11.4677184</v>
+      </c>
+      <c r="O93">
+        <v>-3.382976928</v>
+      </c>
+      <c r="P93">
+        <v>-8.084741472000003</v>
+      </c>
+      <c r="Q93">
+        <v>-4.944741472000003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9515400341716258</v>
+      </c>
+      <c r="T93">
+        <v>10.52379000851904</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.1114191108976356</v>
+      </c>
+      <c r="W93">
+        <v>0.2121931163176446</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3776919013479173</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2807343389245029</v>
+      </c>
+      <c r="C94">
+        <v>-41.05160492686407</v>
+      </c>
+      <c r="D94">
+        <v>25.36439507313596</v>
+      </c>
+      <c r="E94">
+        <v>29.31600000000002</v>
+      </c>
+      <c r="F94">
+        <v>78.01600000000002</v>
+      </c>
+      <c r="G94">
+        <v>11.6</v>
+      </c>
+      <c r="H94">
+        <v>36.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>10.1</v>
+      </c>
+      <c r="K94">
+        <v>3.14</v>
+      </c>
+      <c r="L94">
+        <v>6.96</v>
+      </c>
+      <c r="M94">
+        <v>18.63022080000001</v>
+      </c>
+      <c r="N94">
+        <v>-11.67022080000001</v>
+      </c>
+      <c r="O94">
+        <v>-3.442715136000001</v>
+      </c>
+      <c r="P94">
+        <v>-8.227505664000006</v>
+      </c>
+      <c r="Q94">
+        <v>-5.087505664000006</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.065632538443079</v>
+      </c>
+      <c r="T94">
+        <v>11.83926375958393</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.1102080336052699</v>
+      </c>
+      <c r="W94">
+        <v>0.2124823215750615</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3735865545941355</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2827343389245029</v>
+      </c>
+      <c r="C95">
+        <v>-42.10756576735063</v>
+      </c>
+      <c r="D95">
+        <v>25.15643423264939</v>
+      </c>
+      <c r="E95">
+        <v>30.16400000000002</v>
+      </c>
+      <c r="F95">
+        <v>78.86400000000002</v>
+      </c>
+      <c r="G95">
+        <v>11.6</v>
+      </c>
+      <c r="H95">
+        <v>36.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>10.1</v>
+      </c>
+      <c r="K95">
+        <v>3.14</v>
+      </c>
+      <c r="L95">
+        <v>6.96</v>
+      </c>
+      <c r="M95">
+        <v>18.8327232</v>
+      </c>
+      <c r="N95">
+        <v>-11.8727232</v>
+      </c>
+      <c r="O95">
+        <v>-3.502453344</v>
+      </c>
+      <c r="P95">
+        <v>-8.370269856000004</v>
+      </c>
+      <c r="Q95">
+        <v>-5.230269856000004</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.212322901077805</v>
+      </c>
+      <c r="T95">
+        <v>13.5305871538102</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.1090230009858584</v>
+      </c>
+      <c r="W95">
+        <v>0.212765307364577</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3695694948673168</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2847343389245029</v>
+      </c>
+      <c r="C96">
+        <v>-43.16014422794837</v>
+      </c>
+      <c r="D96">
+        <v>24.95185577205165</v>
+      </c>
+      <c r="E96">
+        <v>31.01200000000001</v>
+      </c>
+      <c r="F96">
+        <v>79.71200000000002</v>
+      </c>
+      <c r="G96">
+        <v>11.6</v>
+      </c>
+      <c r="H96">
+        <v>36.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>10.1</v>
+      </c>
+      <c r="K96">
+        <v>3.14</v>
+      </c>
+      <c r="L96">
+        <v>6.96</v>
+      </c>
+      <c r="M96">
+        <v>19.0352256</v>
+      </c>
+      <c r="N96">
+        <v>-12.0752256</v>
+      </c>
+      <c r="O96">
+        <v>-3.562191552</v>
+      </c>
+      <c r="P96">
+        <v>-8.513034048000003</v>
+      </c>
+      <c r="Q96">
+        <v>-5.373034048000004</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.407910051257439</v>
+      </c>
+      <c r="T96">
+        <v>15.78568501277857</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.1078631818264344</v>
+      </c>
+      <c r="W96">
+        <v>0.2130422721798475</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.365637904496388</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2867343389245029</v>
+      </c>
+      <c r="C97">
+        <v>-44.20942216210052</v>
+      </c>
+      <c r="D97">
+        <v>24.7505778378995</v>
+      </c>
+      <c r="E97">
+        <v>31.86000000000001</v>
+      </c>
+      <c r="F97">
+        <v>80.56000000000002</v>
+      </c>
+      <c r="G97">
+        <v>11.6</v>
+      </c>
+      <c r="H97">
+        <v>36.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>10.1</v>
+      </c>
+      <c r="K97">
+        <v>3.14</v>
+      </c>
+      <c r="L97">
+        <v>6.96</v>
+      </c>
+      <c r="M97">
+        <v>19.237728</v>
+      </c>
+      <c r="N97">
+        <v>-12.277728</v>
+      </c>
+      <c r="O97">
+        <v>-3.62192976</v>
+      </c>
+      <c r="P97">
+        <v>-8.655798240000003</v>
+      </c>
+      <c r="Q97">
+        <v>-5.515798240000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.681732061508928</v>
+      </c>
+      <c r="T97">
+        <v>18.9428220153343</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.1067277799124719</v>
+      </c>
+      <c r="W97">
+        <v>0.2133134061569017</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3617890844490576</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.288734338924503</v>
+      </c>
+      <c r="C98">
+        <v>-45.25547880325197</v>
+      </c>
+      <c r="D98">
+        <v>24.55252119674803</v>
+      </c>
+      <c r="E98">
+        <v>32.708</v>
+      </c>
+      <c r="F98">
+        <v>81.408</v>
+      </c>
+      <c r="G98">
+        <v>11.6</v>
+      </c>
+      <c r="H98">
+        <v>36.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>10.1</v>
+      </c>
+      <c r="K98">
+        <v>3.14</v>
+      </c>
+      <c r="L98">
+        <v>6.96</v>
+      </c>
+      <c r="M98">
+        <v>19.4402304</v>
+      </c>
+      <c r="N98">
+        <v>-12.4802304</v>
+      </c>
+      <c r="O98">
+        <v>-3.681667967999999</v>
+      </c>
+      <c r="P98">
+        <v>-8.798562432000001</v>
+      </c>
+      <c r="Q98">
+        <v>-5.658562432000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.092465076886155</v>
+      </c>
+      <c r="T98">
+        <v>23.67852751916782</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.1056160322050504</v>
+      </c>
+      <c r="W98">
+        <v>0.213578891509434</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3580204481527133</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.290734338924503</v>
+      </c>
+      <c r="C99">
+        <v>-46.29839086884463</v>
+      </c>
+      <c r="D99">
+        <v>24.35760913115538</v>
+      </c>
+      <c r="E99">
+        <v>33.55600000000001</v>
+      </c>
+      <c r="F99">
+        <v>82.25600000000001</v>
+      </c>
+      <c r="G99">
+        <v>11.6</v>
+      </c>
+      <c r="H99">
+        <v>36.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>10.1</v>
+      </c>
+      <c r="K99">
+        <v>3.14</v>
+      </c>
+      <c r="L99">
+        <v>6.96</v>
+      </c>
+      <c r="M99">
+        <v>19.6427328</v>
+      </c>
+      <c r="N99">
+        <v>-12.6827328</v>
+      </c>
+      <c r="O99">
+        <v>-3.741406176</v>
+      </c>
+      <c r="P99">
+        <v>-8.941326624000004</v>
+      </c>
+      <c r="Q99">
+        <v>-5.801326624000004</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.777020102514875</v>
+      </c>
+      <c r="T99">
+        <v>31.5713700255571</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.1045272071307715</v>
+      </c>
+      <c r="W99">
+        <v>0.2138389029371718</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3543295156975306</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2927343389245029</v>
+      </c>
+      <c r="C100">
+        <v>-47.33823265939819</v>
+      </c>
+      <c r="D100">
+        <v>24.16576734060182</v>
+      </c>
+      <c r="E100">
+        <v>34.40400000000001</v>
+      </c>
+      <c r="F100">
+        <v>83.10400000000001</v>
+      </c>
+      <c r="G100">
+        <v>11.6</v>
+      </c>
+      <c r="H100">
+        <v>36.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>10.1</v>
+      </c>
+      <c r="K100">
+        <v>3.14</v>
+      </c>
+      <c r="L100">
+        <v>6.96</v>
+      </c>
+      <c r="M100">
+        <v>19.8452352</v>
+      </c>
+      <c r="N100">
+        <v>-12.8852352</v>
+      </c>
+      <c r="O100">
+        <v>-3.801144384</v>
+      </c>
+      <c r="P100">
+        <v>-9.084090816000003</v>
+      </c>
+      <c r="Q100">
+        <v>-5.944090816000004</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.146130153772311</v>
+      </c>
+      <c r="T100">
+        <v>47.35705503833564</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.1034606029763759</v>
+      </c>
+      <c r="W100">
+        <v>0.2140936080092415</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3507139083944946</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2947343389245029</v>
+      </c>
+      <c r="C101">
+        <v>-48.37507615294543</v>
+      </c>
+      <c r="D101">
+        <v>23.97692384705459</v>
+      </c>
+      <c r="E101">
+        <v>35.25200000000001</v>
+      </c>
+      <c r="F101">
+        <v>83.95200000000001</v>
+      </c>
+      <c r="G101">
+        <v>11.6</v>
+      </c>
+      <c r="H101">
+        <v>36.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>10.1</v>
+      </c>
+      <c r="K101">
+        <v>3.14</v>
+      </c>
+      <c r="L101">
+        <v>6.96</v>
+      </c>
+      <c r="M101">
+        <v>20.0477376</v>
+      </c>
+      <c r="N101">
+        <v>-13.0877376</v>
+      </c>
+      <c r="O101">
+        <v>-3.860882592</v>
+      </c>
+      <c r="P101">
+        <v>-9.226855008000005</v>
+      </c>
+      <c r="Q101">
+        <v>-6.086855008000005</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.253460307544621</v>
+      </c>
+      <c r="T101">
+        <v>94.71411007667128</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.1024155463806549</v>
+      </c>
+      <c r="W101">
+        <v>0.2143431675242996</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3471713436632371</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
